--- a/ohdsi_evidence_master.xlsx
+++ b/ohdsi_evidence_master.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hoffmanka/Documents/ohdsi-trendradar/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hoffmanka/Documents/global-ohdsi-trend-radar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{272AB027-B8CF-CA44-9593-8C358C086E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA08857-32A7-664A-856D-EEF747B18199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="1600" windowWidth="27440" windowHeight="16240" activeTab="1" xr2:uid="{7C8A2B68-97F5-8140-881C-F3FE36F39AA2}"/>
+    <workbookView xWindow="0" yWindow="1600" windowWidth="29240" windowHeight="16240" xr2:uid="{7C8A2B68-97F5-8140-881C-F3FE36F39AA2}"/>
   </bookViews>
   <sheets>
     <sheet name="ohdsi_evidence_master" sheetId="5" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ohdsi_evidence_master!$A$1:$F$602</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,6 +31,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2444" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2562" uniqueCount="1009">
   <si>
     <t>Year</t>
   </si>
@@ -2168,72 +2169,15 @@
     <t>Pulmonology</t>
   </si>
   <si>
-    <t>Oncology; Medication Data</t>
-  </si>
-  <si>
-    <t>Infectious Diseases; Antibiotic Use; Pharmacoepidemiology</t>
-  </si>
-  <si>
-    <t>Geospatial Data; Environmental Exposures</t>
-  </si>
-  <si>
-    <t>Nursing; Clinical Observations</t>
-  </si>
-  <si>
-    <t>Stroke; Rehabilitation</t>
-  </si>
-  <si>
     <t>Exposomics; Environmental Health</t>
   </si>
   <si>
-    <t>Wearables; Patient-Generated Health Data; Digital Health</t>
-  </si>
-  <si>
-    <t>Research Networks; Community Building</t>
-  </si>
-  <si>
-    <t>Learning Health Systems; Clinical Informatics</t>
-  </si>
-  <si>
-    <t>Oncology; Translational Medicine</t>
-  </si>
-  <si>
-    <t>Ophthalmology; Visual Acuity</t>
-  </si>
-  <si>
-    <t>Cardiovascular Medicine; Data Quality</t>
-  </si>
-  <si>
-    <t>Sarcoidosis; Data Quality</t>
-  </si>
-  <si>
-    <t>Clinical Research; FHIR; Data Integration</t>
-  </si>
-  <si>
-    <t>Trauma Care; Registry Data</t>
-  </si>
-  <si>
-    <t>Genomics; Data Quality; Data Curation</t>
-  </si>
-  <si>
     <t>Pediatrics</t>
   </si>
   <si>
-    <t>Patient-Reported Outcomes; Quality of Life</t>
-  </si>
-  <si>
-    <t>Oncology; Anatomy Terminology</t>
-  </si>
-  <si>
-    <t>Oncology; Synthetic Data</t>
-  </si>
-  <si>
     <t>Neurology; Alzheimer’s Disease</t>
   </si>
   <si>
-    <t>Microbiology; Antimicrobial Susceptibility</t>
-  </si>
-  <si>
     <t>Ophthalmology</t>
   </si>
   <si>
@@ -2246,12 +2190,6 @@
     <t>Cardiovascular Medicine; Pharmacoepidemiology</t>
   </si>
   <si>
-    <t>Clinical Trials &amp; Patient Recruitment</t>
-  </si>
-  <si>
-    <t>Alzheimer’s Disease</t>
-  </si>
-  <si>
     <t>Oncology; Geriatrics</t>
   </si>
   <si>
@@ -2609,9 +2547,6 @@
     <t>Software, Tools &amp; Research Workflows; Governance &amp; Regulatory Requirements; Clinical Applications &amp; Real-World Evidence</t>
   </si>
   <si>
-    <t>Phenotyping &amp; Cohort Definition; Clinical Applications &amp; Real-World Evidence</t>
-  </si>
-  <si>
     <t>Specialized &amp; Multimodal Data; Statistical Methods &amp; Causal Inference; AI, LLMs &amp; Natural Language Processing</t>
   </si>
   <si>
@@ -2636,18 +2571,6 @@
     <t>AI, LLMs &amp; Natural Language Processing; Software, Tools &amp; Research Workflows; Clinical Applications &amp; Real-World Evidence</t>
   </si>
   <si>
-    <t>Statistical Methods &amp; Causal Inference; AI, LLMs &amp; Natural Language Processing</t>
-  </si>
-  <si>
-    <t>Data Standardization &amp; OMOP CDM; Terminologies &amp; Semantic Mapping; Privacy &amp; Secure Computing</t>
-  </si>
-  <si>
-    <t>Data Standardization &amp; OMOP CDM; Prediction &amp; Machine Learning</t>
-  </si>
-  <si>
-    <t>Data Standardization &amp; OMOP CDM; Interoperability &amp; Data Integration; Phenotyping &amp; Cohort Definition; AI, LLMs &amp; Natural Language Processing</t>
-  </si>
-  <si>
     <t>Data Standardization &amp; OMOP CDM; Terminologies &amp; Semantic Mapping; Data Quality &amp; Characterization</t>
   </si>
   <si>
@@ -2715,16 +2638,453 @@
   </si>
   <si>
     <t>Applied observational research, real-world evidence, clinical outcomes and use of OHDSI methods in studies.</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-161/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-162/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-163/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-160/</t>
+  </si>
+  <si>
+    <t>Pharmacoepidemiology; Covid-19</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-159/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-158/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-157/</t>
+  </si>
+  <si>
+    <t>Microbiology</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-156/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-155/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-154/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-153/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-152/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-151/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-150/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-149/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-148/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-147/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-146/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-145/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-144/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-143/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-141/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-142/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-140/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-138/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-139/</t>
+  </si>
+  <si>
+    <t>Software, Tools &amp; Research Workflows; Phenotyping &amp; Cohort Definition; AI, LLMs &amp; Natural Language Processing</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-137/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-136/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-135/</t>
+  </si>
+  <si>
+    <t>AI, LLMs &amp; Natural Language Processing; Clinical Applications &amp; Real-World Evidence; Software, Tools &amp; Research Workflows</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-134/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-133/</t>
+  </si>
+  <si>
+    <t>Data Standardization &amp; OMOP CDM; Prediction &amp; Machine Learning; Software, Tools &amp; Research Workflows</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-132/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-131/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-130/</t>
+  </si>
+  <si>
+    <t>Data Standardization &amp; OMOP CDM; Terminologies &amp; Semantic Mapping; Privacy &amp; Secure Computing; Software, Tools &amp; Research Workflows</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-128/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-129/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-127/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-126/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-125/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Standardization &amp; OMOP CDM; Terminologies &amp; Semantic Mapping; </t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-124/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-123/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-122/</t>
+  </si>
+  <si>
+    <t>Link to Abstract</t>
+  </si>
+  <si>
+    <t>AI, LLMs &amp; Natural Language Processing; Phenotyping &amp; Cohort Definition</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-121/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-120/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-119/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-118/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-117/</t>
+  </si>
+  <si>
+    <t>Software, Tools &amp; Research Workflows; AI, LLMs &amp; Natural Language Processing</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-116/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-115/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-114/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-113/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-112/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-111/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-110/</t>
+  </si>
+  <si>
+    <t>Data Quality &amp; Characterization; AI, LLMs &amp; Natural Language Processing</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-109/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-108/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-107/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-106/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-105/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-104/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-103/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-102/</t>
+  </si>
+  <si>
+    <t>AI, LLMs &amp; Natural Language Processing; Data Standardization &amp; OMOP CDM; Terminologies &amp; Semantic Mapping</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-101/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-100/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-99/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-98/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-97/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-96/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-95/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-94/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-93/</t>
+  </si>
+  <si>
+    <t>Data Standardization &amp; OMOP CDM; Terminologies &amp; Semantic Mapping; Specialized &amp; Multimodal Data</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-92/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-91/</t>
+  </si>
+  <si>
+    <t>Pediatrics; Rare Diseases</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-90/</t>
+  </si>
+  <si>
+    <t>Data Standardization &amp; OMOP CDM; Data Quality &amp; Characterization; Software, Tools &amp; Research Workflows; AI, LLMs &amp; Natural Language Processing</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-88/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-89/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-87/</t>
+  </si>
+  <si>
+    <t>Internal Medicine</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-86/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-85/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-82/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-83/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-84/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-81/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-80/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-79/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-78/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-77/</t>
+  </si>
+  <si>
+    <t>Neurology; Stroke</t>
+  </si>
+  <si>
+    <t>Military Health Services Research; Trauma</t>
+  </si>
+  <si>
+    <t>Pediatrics; Environmental Health</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-76/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-75/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-74/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-73/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-72/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-71/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-70/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-69/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-68/</t>
+  </si>
+  <si>
+    <t>Environmental Health</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-67/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-66/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-65/</t>
+  </si>
+  <si>
+    <t>Infectious Diseases; Pharmacoepidemiology</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-64/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-63/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-62/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-61/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-60/</t>
+  </si>
+  <si>
+    <t>Maternal and Perinatal Health; Women's Health</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-59/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-58/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-57/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-56/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-55/</t>
+  </si>
+  <si>
+    <t>Pharmacoepidemiology; Diabetes</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-54/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-53/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-52/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2026showcase-51/</t>
+  </si>
+  <si>
+    <t>Phenotyping &amp; Cohort Definition; Clinical Applications &amp; Real-World Evidence; AI, LLMs &amp; Natural Language Processing</t>
+  </si>
+  <si>
+    <t>Clinical Applications &amp; Real-World Evidence; AI, LLMs &amp; Natural Language Processing</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2023showcase-2/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2023showcase-3/</t>
+  </si>
+  <si>
+    <t>COVID-19; Infectious Diseases; Pharmacoepidemiology</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2024showcase-1/</t>
+  </si>
+  <si>
+    <t>https://www.ohdsi.org/2025showcase-1/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2775,17 +3135,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3098,16 +3461,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68ABCD33-977E-804C-B8A3-208F8BF35AB9}">
-  <dimension ref="A1:F602"/>
+  <dimension ref="A1:G605"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="43.5" customWidth="1"/>
-    <col min="4" max="4" width="41.1640625" customWidth="1"/>
-    <col min="5" max="5" width="65.1640625" customWidth="1"/>
-    <col min="6" max="6" width="54.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" customWidth="1"/>
+    <col min="4" max="4" width="53.5" customWidth="1"/>
+    <col min="5" max="5" width="69" customWidth="1"/>
+    <col min="6" max="6" width="36.33203125" customWidth="1"/>
+    <col min="7" max="7" width="38.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3126,8 +3490,11 @@
       <c r="F1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2023</v>
       </c>
@@ -3141,13 +3508,16 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>766</v>
+        <v>825</v>
       </c>
       <c r="F2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G2" s="3" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2023</v>
       </c>
@@ -3161,13 +3531,16 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F3" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>1006</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2023</v>
       </c>
@@ -3181,13 +3554,13 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F4" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2023</v>
       </c>
@@ -3201,13 +3574,13 @@
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2023</v>
       </c>
@@ -3221,13 +3594,13 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2023</v>
       </c>
@@ -3241,13 +3614,13 @@
         <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2023</v>
       </c>
@@ -3261,13 +3634,13 @@
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F8" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -3281,13 +3654,13 @@
         <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>770</v>
+        <v>749</v>
       </c>
       <c r="F9" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>2023</v>
       </c>
@@ -3301,13 +3674,13 @@
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2023</v>
       </c>
@@ -3321,13 +3694,13 @@
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2023</v>
       </c>
@@ -3341,13 +3714,13 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F12" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2023</v>
       </c>
@@ -3361,13 +3734,13 @@
         <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F13" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2023</v>
       </c>
@@ -3381,13 +3754,13 @@
         <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F14" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2023</v>
       </c>
@@ -3401,13 +3774,13 @@
         <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F15" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>2023</v>
       </c>
@@ -3421,7 +3794,7 @@
         <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F16" t="s">
         <v>55</v>
@@ -3441,7 +3814,7 @@
         <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>771</v>
+        <v>750</v>
       </c>
       <c r="F17" t="s">
         <v>59</v>
@@ -3461,7 +3834,7 @@
         <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F18" t="s">
         <v>55</v>
@@ -3481,7 +3854,7 @@
         <v>27</v>
       </c>
       <c r="E19" t="s">
-        <v>773</v>
+        <v>752</v>
       </c>
       <c r="F19" t="s">
         <v>55</v>
@@ -3501,7 +3874,7 @@
         <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F20" t="s">
         <v>55</v>
@@ -3521,7 +3894,7 @@
         <v>29</v>
       </c>
       <c r="E21" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="F21" t="s">
         <v>61</v>
@@ -3541,7 +3914,7 @@
         <v>30</v>
       </c>
       <c r="E22" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="F22" t="s">
         <v>55</v>
@@ -3561,10 +3934,10 @@
         <v>31</v>
       </c>
       <c r="E23" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F23" t="s">
-        <v>742</v>
+        <v>721</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -3581,7 +3954,7 @@
         <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="F24" t="s">
         <v>55</v>
@@ -3601,7 +3974,7 @@
         <v>33</v>
       </c>
       <c r="E25" t="s">
-        <v>777</v>
+        <v>756</v>
       </c>
       <c r="F25" t="s">
         <v>55</v>
@@ -3621,7 +3994,7 @@
         <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>55</v>
@@ -3641,7 +4014,7 @@
         <v>35</v>
       </c>
       <c r="E27" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F27" t="s">
         <v>195</v>
@@ -3661,7 +4034,7 @@
         <v>36</v>
       </c>
       <c r="E28" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>55</v>
@@ -3681,7 +4054,7 @@
         <v>37</v>
       </c>
       <c r="E29" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F29" t="s">
         <v>55</v>
@@ -3701,7 +4074,7 @@
         <v>38</v>
       </c>
       <c r="E30" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F30" t="s">
         <v>195</v>
@@ -3721,7 +4094,7 @@
         <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F31" t="s">
         <v>62</v>
@@ -3741,7 +4114,7 @@
         <v>40</v>
       </c>
       <c r="E32" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>55</v>
@@ -3761,7 +4134,7 @@
         <v>41</v>
       </c>
       <c r="E33" t="s">
-        <v>779</v>
+        <v>758</v>
       </c>
       <c r="F33" t="s">
         <v>55</v>
@@ -3781,7 +4154,7 @@
         <v>42</v>
       </c>
       <c r="E34" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>55</v>
@@ -3801,7 +4174,7 @@
         <v>43</v>
       </c>
       <c r="E35" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F35" t="s">
         <v>63</v>
@@ -3821,7 +4194,7 @@
         <v>44</v>
       </c>
       <c r="E36" t="s">
-        <v>780</v>
+        <v>759</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>55</v>
@@ -3841,7 +4214,7 @@
         <v>45</v>
       </c>
       <c r="E37" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>55</v>
@@ -3861,7 +4234,7 @@
         <v>46</v>
       </c>
       <c r="E38" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F38" t="s">
         <v>64</v>
@@ -3881,7 +4254,7 @@
         <v>47</v>
       </c>
       <c r="E39" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F39" t="s">
         <v>65</v>
@@ -3921,7 +4294,7 @@
         <v>49</v>
       </c>
       <c r="E41" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F41" t="s">
         <v>68</v>
@@ -3941,7 +4314,7 @@
         <v>50</v>
       </c>
       <c r="E42" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>55</v>
@@ -3961,7 +4334,7 @@
         <v>51</v>
       </c>
       <c r="E43" t="s">
-        <v>781</v>
+        <v>760</v>
       </c>
       <c r="F43" t="s">
         <v>55</v>
@@ -3981,7 +4354,7 @@
         <v>69</v>
       </c>
       <c r="E44" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F44" t="s">
         <v>70</v>
@@ -4001,7 +4374,7 @@
         <v>71</v>
       </c>
       <c r="E45" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>55</v>
@@ -4041,7 +4414,7 @@
         <v>73</v>
       </c>
       <c r="E47" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F47" t="s">
         <v>55</v>
@@ -4061,7 +4434,7 @@
         <v>74</v>
       </c>
       <c r="E48" t="s">
-        <v>783</v>
+        <v>762</v>
       </c>
       <c r="F48" t="s">
         <v>55</v>
@@ -4081,7 +4454,7 @@
         <v>75</v>
       </c>
       <c r="E49" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F49" t="s">
         <v>195</v>
@@ -4101,7 +4474,7 @@
         <v>76</v>
       </c>
       <c r="E50" t="s">
-        <v>784</v>
+        <v>763</v>
       </c>
       <c r="F50" t="s">
         <v>55</v>
@@ -4141,7 +4514,7 @@
         <v>79</v>
       </c>
       <c r="E52" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F52" t="s">
         <v>55</v>
@@ -4161,7 +4534,7 @@
         <v>80</v>
       </c>
       <c r="E53" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F53" t="s">
         <v>55</v>
@@ -4181,7 +4554,7 @@
         <v>81</v>
       </c>
       <c r="E54" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F54" t="s">
         <v>82</v>
@@ -4201,10 +4574,10 @@
         <v>83</v>
       </c>
       <c r="E55" t="s">
-        <v>785</v>
+        <v>764</v>
       </c>
       <c r="F55" t="s">
-        <v>739</v>
+        <v>718</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
@@ -4221,7 +4594,7 @@
         <v>84</v>
       </c>
       <c r="E56" t="s">
-        <v>784</v>
+        <v>763</v>
       </c>
       <c r="F56" t="s">
         <v>55</v>
@@ -4261,7 +4634,7 @@
         <v>87</v>
       </c>
       <c r="E58" t="s">
-        <v>785</v>
+        <v>764</v>
       </c>
       <c r="F58" t="s">
         <v>55</v>
@@ -4301,7 +4674,7 @@
         <v>89</v>
       </c>
       <c r="E60" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F60" t="s">
         <v>90</v>
@@ -4321,7 +4694,7 @@
         <v>91</v>
       </c>
       <c r="E61" t="s">
-        <v>786</v>
+        <v>765</v>
       </c>
       <c r="F61" t="s">
         <v>55</v>
@@ -4381,7 +4754,7 @@
         <v>95</v>
       </c>
       <c r="E64" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F64" t="s">
         <v>55</v>
@@ -4401,7 +4774,7 @@
         <v>96</v>
       </c>
       <c r="E65" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F65" t="s">
         <v>55</v>
@@ -4421,10 +4794,10 @@
         <v>97</v>
       </c>
       <c r="E66" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F66" t="s">
-        <v>743</v>
+        <v>722</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
@@ -4461,10 +4834,10 @@
         <v>100</v>
       </c>
       <c r="E68" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F68" t="s">
-        <v>755</v>
+        <v>734</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
@@ -4481,7 +4854,7 @@
         <v>101</v>
       </c>
       <c r="E69" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F69" t="s">
         <v>55</v>
@@ -4501,7 +4874,7 @@
         <v>102</v>
       </c>
       <c r="E70" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F70" t="s">
         <v>55</v>
@@ -4521,7 +4894,7 @@
         <v>103</v>
       </c>
       <c r="E71" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F71" t="s">
         <v>55</v>
@@ -4541,7 +4914,7 @@
         <v>104</v>
       </c>
       <c r="E72" t="s">
-        <v>784</v>
+        <v>763</v>
       </c>
       <c r="F72" t="s">
         <v>55</v>
@@ -4561,7 +4934,7 @@
         <v>105</v>
       </c>
       <c r="E73" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F73" t="s">
         <v>55</v>
@@ -4581,7 +4954,7 @@
         <v>106</v>
       </c>
       <c r="E74" t="s">
-        <v>784</v>
+        <v>763</v>
       </c>
       <c r="F74" t="s">
         <v>55</v>
@@ -4601,7 +4974,7 @@
         <v>107</v>
       </c>
       <c r="E75" t="s">
-        <v>784</v>
+        <v>763</v>
       </c>
       <c r="F75" t="s">
         <v>55</v>
@@ -4621,7 +4994,7 @@
         <v>108</v>
       </c>
       <c r="E76" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F76" t="s">
         <v>55</v>
@@ -4641,7 +5014,7 @@
         <v>109</v>
       </c>
       <c r="E77" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F77" t="s">
         <v>55</v>
@@ -4721,7 +5094,7 @@
         <v>114</v>
       </c>
       <c r="E81" t="s">
-        <v>787</v>
+        <v>766</v>
       </c>
       <c r="F81" t="s">
         <v>55</v>
@@ -4741,7 +5114,7 @@
         <v>115</v>
       </c>
       <c r="E82" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F82" t="s">
         <v>55</v>
@@ -4761,7 +5134,7 @@
         <v>116</v>
       </c>
       <c r="E83" t="s">
-        <v>788</v>
+        <v>767</v>
       </c>
       <c r="F83" t="s">
         <v>55</v>
@@ -4781,7 +5154,7 @@
         <v>117</v>
       </c>
       <c r="E84" t="s">
-        <v>789</v>
+        <v>768</v>
       </c>
       <c r="F84" t="s">
         <v>55</v>
@@ -4801,7 +5174,7 @@
         <v>118</v>
       </c>
       <c r="E85" t="s">
-        <v>790</v>
+        <v>769</v>
       </c>
       <c r="F85" t="s">
         <v>119</v>
@@ -4821,7 +5194,7 @@
         <v>120</v>
       </c>
       <c r="E86" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="F86" t="s">
         <v>121</v>
@@ -4901,7 +5274,7 @@
         <v>127</v>
       </c>
       <c r="E90" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="F90" t="s">
         <v>55</v>
@@ -4961,7 +5334,7 @@
         <v>133</v>
       </c>
       <c r="E93" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="F93" t="s">
         <v>55</v>
@@ -5101,7 +5474,7 @@
         <v>145</v>
       </c>
       <c r="E100" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="F100" t="s">
         <v>55</v>
@@ -5121,7 +5494,7 @@
         <v>146</v>
       </c>
       <c r="E101" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F101" t="s">
         <v>147</v>
@@ -5284,7 +5657,7 @@
         <v>131</v>
       </c>
       <c r="F109" t="s">
-        <v>759</v>
+        <v>738</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
@@ -5301,7 +5674,7 @@
         <v>162</v>
       </c>
       <c r="E110" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F110" t="s">
         <v>55</v>
@@ -5321,10 +5694,10 @@
         <v>163</v>
       </c>
       <c r="E111" t="s">
-        <v>792</v>
+        <v>771</v>
       </c>
       <c r="F111" t="s">
-        <v>758</v>
+        <v>737</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
@@ -5461,7 +5834,7 @@
         <v>176</v>
       </c>
       <c r="E118" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="F118" t="s">
         <v>177</v>
@@ -5504,7 +5877,7 @@
         <v>131</v>
       </c>
       <c r="F120" t="s">
-        <v>754</v>
+        <v>733</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
@@ -5521,7 +5894,7 @@
         <v>181</v>
       </c>
       <c r="E121" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F121" t="s">
         <v>65</v>
@@ -5541,7 +5914,7 @@
         <v>182</v>
       </c>
       <c r="E122" t="s">
-        <v>793</v>
+        <v>772</v>
       </c>
       <c r="F122" t="s">
         <v>183</v>
@@ -5561,7 +5934,7 @@
         <v>184</v>
       </c>
       <c r="E123" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F123" t="s">
         <v>185</v>
@@ -5601,7 +5974,7 @@
         <v>187</v>
       </c>
       <c r="E125" t="s">
-        <v>794</v>
+        <v>773</v>
       </c>
       <c r="F125" t="s">
         <v>188</v>
@@ -5624,7 +5997,7 @@
         <v>131</v>
       </c>
       <c r="F126" t="s">
-        <v>761</v>
+        <v>740</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
@@ -5664,7 +6037,7 @@
         <v>131</v>
       </c>
       <c r="F128" t="s">
-        <v>740</v>
+        <v>719</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
@@ -5681,7 +6054,7 @@
         <v>193</v>
       </c>
       <c r="E129" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="F129" t="s">
         <v>55</v>
@@ -5721,7 +6094,7 @@
         <v>196</v>
       </c>
       <c r="E131" t="s">
-        <v>789</v>
+        <v>768</v>
       </c>
       <c r="F131" t="s">
         <v>55</v>
@@ -5781,7 +6154,7 @@
         <v>199</v>
       </c>
       <c r="E134" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="F134" t="s">
         <v>59</v>
@@ -5841,7 +6214,7 @@
         <v>202</v>
       </c>
       <c r="E137" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F137" t="s">
         <v>55</v>
@@ -5861,7 +6234,7 @@
         <v>203</v>
       </c>
       <c r="E138" t="s">
-        <v>789</v>
+        <v>768</v>
       </c>
       <c r="F138" t="s">
         <v>55</v>
@@ -5921,7 +6294,7 @@
         <v>207</v>
       </c>
       <c r="E141" t="s">
-        <v>795</v>
+        <v>774</v>
       </c>
       <c r="F141" t="s">
         <v>208</v>
@@ -6001,7 +6374,7 @@
         <v>213</v>
       </c>
       <c r="E145" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F145" t="s">
         <v>214</v>
@@ -6021,7 +6394,7 @@
         <v>215</v>
       </c>
       <c r="E146" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="F146" t="s">
         <v>55</v>
@@ -6061,7 +6434,7 @@
         <v>217</v>
       </c>
       <c r="E148" t="s">
-        <v>796</v>
+        <v>775</v>
       </c>
       <c r="F148" t="s">
         <v>55</v>
@@ -6101,7 +6474,7 @@
         <v>219</v>
       </c>
       <c r="E150" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="F150" t="s">
         <v>220</v>
@@ -6121,7 +6494,7 @@
         <v>221</v>
       </c>
       <c r="E151" t="s">
-        <v>797</v>
+        <v>776</v>
       </c>
       <c r="F151" t="s">
         <v>220</v>
@@ -6161,7 +6534,7 @@
         <v>224</v>
       </c>
       <c r="E153" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="F153" t="s">
         <v>55</v>
@@ -6201,7 +6574,7 @@
         <v>226</v>
       </c>
       <c r="E155" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="F155" t="s">
         <v>227</v>
@@ -6221,7 +6594,7 @@
         <v>228</v>
       </c>
       <c r="E156" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F156" t="s">
         <v>229</v>
@@ -6261,7 +6634,7 @@
         <v>231</v>
       </c>
       <c r="E158" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F158" t="s">
         <v>232</v>
@@ -6307,7 +6680,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>2023</v>
       </c>
@@ -6324,10 +6697,10 @@
         <v>131</v>
       </c>
       <c r="F161" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>2023</v>
       </c>
@@ -6341,13 +6714,13 @@
         <v>237</v>
       </c>
       <c r="E162" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F162" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>2024</v>
       </c>
@@ -6361,13 +6734,16 @@
         <v>239</v>
       </c>
       <c r="E163" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F163" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G163" s="3" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>2024</v>
       </c>
@@ -6381,13 +6757,13 @@
         <v>240</v>
       </c>
       <c r="E164" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="F164" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>2024</v>
       </c>
@@ -6401,13 +6777,13 @@
         <v>242</v>
       </c>
       <c r="E165" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F165" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>2024</v>
       </c>
@@ -6421,13 +6797,13 @@
         <v>243</v>
       </c>
       <c r="E166" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="F166" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>2024</v>
       </c>
@@ -6441,13 +6817,13 @@
         <v>245</v>
       </c>
       <c r="E167" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F167" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>2024</v>
       </c>
@@ -6461,13 +6837,13 @@
         <v>246</v>
       </c>
       <c r="E168" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F168" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>2024</v>
       </c>
@@ -6481,13 +6857,13 @@
         <v>247</v>
       </c>
       <c r="E169" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F169" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>2024</v>
       </c>
@@ -6501,13 +6877,13 @@
         <v>248</v>
       </c>
       <c r="E170" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F170" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>2024</v>
       </c>
@@ -6521,13 +6897,13 @@
         <v>249</v>
       </c>
       <c r="E171" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F171" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>2024</v>
       </c>
@@ -6541,13 +6917,13 @@
         <v>250</v>
       </c>
       <c r="E172" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F172" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>2024</v>
       </c>
@@ -6561,13 +6937,13 @@
         <v>251</v>
       </c>
       <c r="E173" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F173" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>2024</v>
       </c>
@@ -6581,13 +6957,13 @@
         <v>252</v>
       </c>
       <c r="E174" t="s">
-        <v>798</v>
+        <v>777</v>
       </c>
       <c r="F174" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>2024</v>
       </c>
@@ -6601,13 +6977,13 @@
         <v>253</v>
       </c>
       <c r="E175" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F175" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>2024</v>
       </c>
@@ -6621,7 +6997,7 @@
         <v>254</v>
       </c>
       <c r="E176" t="s">
-        <v>799</v>
+        <v>778</v>
       </c>
       <c r="F176" t="s">
         <v>55</v>
@@ -6641,7 +7017,7 @@
         <v>255</v>
       </c>
       <c r="E177" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F177" t="s">
         <v>470</v>
@@ -6661,7 +7037,7 @@
         <v>256</v>
       </c>
       <c r="E178" t="s">
-        <v>800</v>
+        <v>779</v>
       </c>
       <c r="F178" t="s">
         <v>55</v>
@@ -6681,7 +7057,7 @@
         <v>257</v>
       </c>
       <c r="E179" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F179" t="s">
         <v>55</v>
@@ -6701,7 +7077,7 @@
         <v>258</v>
       </c>
       <c r="E180" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F180" t="s">
         <v>55</v>
@@ -6721,10 +7097,10 @@
         <v>259</v>
       </c>
       <c r="E181" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="F181" t="s">
-        <v>731</v>
+        <v>712</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.2">
@@ -6741,10 +7117,10 @@
         <v>260</v>
       </c>
       <c r="E182" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F182" t="s">
-        <v>747</v>
+        <v>726</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.2">
@@ -6761,7 +7137,7 @@
         <v>261</v>
       </c>
       <c r="E183" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F183" t="s">
         <v>262</v>
@@ -6781,7 +7157,7 @@
         <v>263</v>
       </c>
       <c r="E184" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F184" t="s">
         <v>55</v>
@@ -6801,7 +7177,7 @@
         <v>264</v>
       </c>
       <c r="E185" t="s">
-        <v>801</v>
+        <v>780</v>
       </c>
       <c r="F185" t="s">
         <v>55</v>
@@ -6821,7 +7197,7 @@
         <v>265</v>
       </c>
       <c r="E186" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F186" t="s">
         <v>55</v>
@@ -6841,7 +7217,7 @@
         <v>266</v>
       </c>
       <c r="E187" t="s">
-        <v>802</v>
+        <v>781</v>
       </c>
       <c r="F187" t="s">
         <v>55</v>
@@ -6861,7 +7237,7 @@
         <v>267</v>
       </c>
       <c r="E188" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F188" t="s">
         <v>195</v>
@@ -6881,7 +7257,7 @@
         <v>268</v>
       </c>
       <c r="E189" t="s">
-        <v>800</v>
+        <v>779</v>
       </c>
       <c r="F189" t="s">
         <v>195</v>
@@ -6901,7 +7277,7 @@
         <v>269</v>
       </c>
       <c r="E190" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="F190" t="s">
         <v>195</v>
@@ -6921,7 +7297,7 @@
         <v>270</v>
       </c>
       <c r="E191" t="s">
-        <v>802</v>
+        <v>781</v>
       </c>
       <c r="F191" t="s">
         <v>55</v>
@@ -6941,7 +7317,7 @@
         <v>271</v>
       </c>
       <c r="E192" t="s">
-        <v>804</v>
+        <v>783</v>
       </c>
       <c r="F192" t="s">
         <v>55</v>
@@ -6961,7 +7337,7 @@
         <v>272</v>
       </c>
       <c r="E193" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F193" t="s">
         <v>262</v>
@@ -6981,7 +7357,7 @@
         <v>273</v>
       </c>
       <c r="E194" t="s">
-        <v>805</v>
+        <v>784</v>
       </c>
       <c r="F194" t="s">
         <v>55</v>
@@ -7001,7 +7377,7 @@
         <v>274</v>
       </c>
       <c r="E195" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F195" t="s">
         <v>55</v>
@@ -7021,7 +7397,7 @@
         <v>275</v>
       </c>
       <c r="E196" t="s">
-        <v>806</v>
+        <v>785</v>
       </c>
       <c r="F196" t="s">
         <v>55</v>
@@ -7041,7 +7417,7 @@
         <v>276</v>
       </c>
       <c r="E197" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F197" t="s">
         <v>55</v>
@@ -7061,10 +7437,10 @@
         <v>277</v>
       </c>
       <c r="E198" t="s">
-        <v>807</v>
+        <v>786</v>
       </c>
       <c r="F198" t="s">
-        <v>731</v>
+        <v>712</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.2">
@@ -7081,7 +7457,7 @@
         <v>278</v>
       </c>
       <c r="E199" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F199" t="s">
         <v>279</v>
@@ -7124,7 +7500,7 @@
         <v>66</v>
       </c>
       <c r="F201" t="s">
-        <v>731</v>
+        <v>712</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.2">
@@ -7161,7 +7537,7 @@
         <v>283</v>
       </c>
       <c r="E203" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="F203" t="s">
         <v>55</v>
@@ -7181,7 +7557,7 @@
         <v>284</v>
       </c>
       <c r="E204" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="F204" t="s">
         <v>55</v>
@@ -7201,7 +7577,7 @@
         <v>285</v>
       </c>
       <c r="E205" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F205" t="s">
         <v>55</v>
@@ -7221,7 +7597,7 @@
         <v>286</v>
       </c>
       <c r="E206" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F206" t="s">
         <v>55</v>
@@ -7241,7 +7617,7 @@
         <v>287</v>
       </c>
       <c r="E207" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F207" t="s">
         <v>55</v>
@@ -7261,7 +7637,7 @@
         <v>288</v>
       </c>
       <c r="E208" t="s">
-        <v>808</v>
+        <v>787</v>
       </c>
       <c r="F208" t="s">
         <v>55</v>
@@ -7281,7 +7657,7 @@
         <v>289</v>
       </c>
       <c r="E209" t="s">
-        <v>809</v>
+        <v>788</v>
       </c>
       <c r="F209" t="s">
         <v>55</v>
@@ -7301,7 +7677,7 @@
         <v>290</v>
       </c>
       <c r="E210" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F210" t="s">
         <v>55</v>
@@ -7321,7 +7697,7 @@
         <v>291</v>
       </c>
       <c r="E211" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F211" t="s">
         <v>55</v>
@@ -7341,7 +7717,7 @@
         <v>292</v>
       </c>
       <c r="E212" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="F212" t="s">
         <v>55</v>
@@ -7361,7 +7737,7 @@
         <v>293</v>
       </c>
       <c r="E213" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F213" t="s">
         <v>55</v>
@@ -7381,7 +7757,7 @@
         <v>294</v>
       </c>
       <c r="E214" t="s">
-        <v>810</v>
+        <v>789</v>
       </c>
       <c r="F214" t="s">
         <v>55</v>
@@ -7404,7 +7780,7 @@
         <v>66</v>
       </c>
       <c r="F215" t="s">
-        <v>762</v>
+        <v>741</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.2">
@@ -7421,10 +7797,10 @@
         <v>296</v>
       </c>
       <c r="E216" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="F216" t="s">
-        <v>759</v>
+        <v>738</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.2">
@@ -7441,7 +7817,7 @@
         <v>297</v>
       </c>
       <c r="E217" t="s">
-        <v>787</v>
+        <v>766</v>
       </c>
       <c r="F217" t="s">
         <v>55</v>
@@ -7461,7 +7837,7 @@
         <v>298</v>
       </c>
       <c r="E218" t="s">
-        <v>805</v>
+        <v>784</v>
       </c>
       <c r="F218" t="s">
         <v>55</v>
@@ -7501,7 +7877,7 @@
         <v>301</v>
       </c>
       <c r="E220" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="F220" t="s">
         <v>302</v>
@@ -7521,7 +7897,7 @@
         <v>303</v>
       </c>
       <c r="E221" t="s">
-        <v>811</v>
+        <v>790</v>
       </c>
       <c r="F221" t="s">
         <v>304</v>
@@ -7541,7 +7917,7 @@
         <v>305</v>
       </c>
       <c r="E222" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F222" t="s">
         <v>55</v>
@@ -7561,7 +7937,7 @@
         <v>306</v>
       </c>
       <c r="E223" t="s">
-        <v>801</v>
+        <v>780</v>
       </c>
       <c r="F223" t="s">
         <v>57</v>
@@ -7581,7 +7957,7 @@
         <v>307</v>
       </c>
       <c r="E224" t="s">
-        <v>812</v>
+        <v>791</v>
       </c>
       <c r="F224" t="s">
         <v>55</v>
@@ -7601,7 +7977,7 @@
         <v>308</v>
       </c>
       <c r="E225" t="s">
-        <v>813</v>
+        <v>792</v>
       </c>
       <c r="F225" t="s">
         <v>55</v>
@@ -7621,7 +7997,7 @@
         <v>309</v>
       </c>
       <c r="E226" t="s">
-        <v>814</v>
+        <v>793</v>
       </c>
       <c r="F226" t="s">
         <v>55</v>
@@ -7641,7 +8017,7 @@
         <v>310</v>
       </c>
       <c r="E227" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="F227" t="s">
         <v>63</v>
@@ -7661,10 +8037,10 @@
         <v>311</v>
       </c>
       <c r="E228" t="s">
-        <v>783</v>
+        <v>762</v>
       </c>
       <c r="F228" t="s">
-        <v>756</v>
+        <v>735</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.2">
@@ -7681,7 +8057,7 @@
         <v>312</v>
       </c>
       <c r="E229" t="s">
-        <v>784</v>
+        <v>763</v>
       </c>
       <c r="F229" t="s">
         <v>55</v>
@@ -7701,7 +8077,7 @@
         <v>313</v>
       </c>
       <c r="E230" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F230" t="s">
         <v>314</v>
@@ -7721,7 +8097,7 @@
         <v>315</v>
       </c>
       <c r="E231" t="s">
-        <v>784</v>
+        <v>763</v>
       </c>
       <c r="F231" t="s">
         <v>55</v>
@@ -7741,7 +8117,7 @@
         <v>316</v>
       </c>
       <c r="E232" t="s">
-        <v>785</v>
+        <v>764</v>
       </c>
       <c r="F232" t="s">
         <v>195</v>
@@ -7761,7 +8137,7 @@
         <v>317</v>
       </c>
       <c r="E233" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F233" t="s">
         <v>55</v>
@@ -7781,10 +8157,10 @@
         <v>318</v>
       </c>
       <c r="E234" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F234" t="s">
-        <v>762</v>
+        <v>741</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.2">
@@ -7801,7 +8177,7 @@
         <v>319</v>
       </c>
       <c r="E235" t="s">
-        <v>815</v>
+        <v>794</v>
       </c>
       <c r="F235" t="s">
         <v>55</v>
@@ -7821,7 +8197,7 @@
         <v>320</v>
       </c>
       <c r="E236" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="F236" t="s">
         <v>55</v>
@@ -7841,7 +8217,7 @@
         <v>321</v>
       </c>
       <c r="E237" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F237" t="s">
         <v>55</v>
@@ -7861,7 +8237,7 @@
         <v>322</v>
       </c>
       <c r="E238" t="s">
-        <v>785</v>
+        <v>764</v>
       </c>
       <c r="F238" t="s">
         <v>55</v>
@@ -7881,10 +8257,10 @@
         <v>323</v>
       </c>
       <c r="E239" t="s">
-        <v>785</v>
+        <v>764</v>
       </c>
       <c r="F239" t="s">
-        <v>731</v>
+        <v>712</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.2">
@@ -7904,7 +8280,7 @@
         <v>131</v>
       </c>
       <c r="F240" t="s">
-        <v>746</v>
+        <v>725</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.2">
@@ -7924,7 +8300,7 @@
         <v>131</v>
       </c>
       <c r="F241" t="s">
-        <v>745</v>
+        <v>724</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.2">
@@ -7964,7 +8340,7 @@
         <v>131</v>
       </c>
       <c r="F243" t="s">
-        <v>745</v>
+        <v>724</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.2">
@@ -7981,10 +8357,10 @@
         <v>328</v>
       </c>
       <c r="E244" t="s">
-        <v>792</v>
+        <v>771</v>
       </c>
       <c r="F244" t="s">
-        <v>748</v>
+        <v>727</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.2">
@@ -8004,7 +8380,7 @@
         <v>131</v>
       </c>
       <c r="F245" t="s">
-        <v>745</v>
+        <v>724</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.2">
@@ -8021,7 +8397,7 @@
         <v>330</v>
       </c>
       <c r="E246" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="F246" t="s">
         <v>279</v>
@@ -8041,7 +8417,7 @@
         <v>331</v>
       </c>
       <c r="E247" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="F247" t="s">
         <v>57</v>
@@ -8061,10 +8437,10 @@
         <v>332</v>
       </c>
       <c r="E248" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="F248" t="s">
-        <v>763</v>
+        <v>742</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.2">
@@ -8081,7 +8457,7 @@
         <v>333</v>
       </c>
       <c r="E249" t="s">
-        <v>814</v>
+        <v>793</v>
       </c>
       <c r="F249" t="s">
         <v>57</v>
@@ -8101,7 +8477,7 @@
         <v>334</v>
       </c>
       <c r="E250" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="F250" t="s">
         <v>262</v>
@@ -8141,7 +8517,7 @@
         <v>337</v>
       </c>
       <c r="E252" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F252" t="s">
         <v>262</v>
@@ -8164,7 +8540,7 @@
         <v>131</v>
       </c>
       <c r="F253" t="s">
-        <v>744</v>
+        <v>723</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.2">
@@ -8244,7 +8620,7 @@
         <v>131</v>
       </c>
       <c r="F257" t="s">
-        <v>764</v>
+        <v>743</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.2">
@@ -8284,7 +8660,7 @@
         <v>131</v>
       </c>
       <c r="F259" t="s">
-        <v>765</v>
+        <v>744</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.2">
@@ -8304,7 +8680,7 @@
         <v>131</v>
       </c>
       <c r="F260" t="s">
-        <v>764</v>
+        <v>743</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.2">
@@ -8321,10 +8697,10 @@
         <v>348</v>
       </c>
       <c r="E261" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="F261" t="s">
-        <v>757</v>
+        <v>736</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.2">
@@ -8361,7 +8737,7 @@
         <v>350</v>
       </c>
       <c r="E263" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="F263" t="s">
         <v>55</v>
@@ -8384,7 +8760,7 @@
         <v>131</v>
       </c>
       <c r="F264" t="s">
-        <v>731</v>
+        <v>712</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.2">
@@ -8401,7 +8777,7 @@
         <v>352</v>
       </c>
       <c r="E265" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F265" t="s">
         <v>55</v>
@@ -8421,7 +8797,7 @@
         <v>353</v>
       </c>
       <c r="E266" t="s">
-        <v>816</v>
+        <v>795</v>
       </c>
       <c r="F266" t="s">
         <v>279</v>
@@ -8461,7 +8837,7 @@
         <v>355</v>
       </c>
       <c r="E268" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F268" t="s">
         <v>55</v>
@@ -8481,7 +8857,7 @@
         <v>356</v>
       </c>
       <c r="E269" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F269" t="s">
         <v>55</v>
@@ -8501,7 +8877,7 @@
         <v>357</v>
       </c>
       <c r="E270" t="s">
-        <v>817</v>
+        <v>796</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>55</v>
@@ -8521,7 +8897,7 @@
         <v>358</v>
       </c>
       <c r="E271" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F271" t="s">
         <v>55</v>
@@ -8561,7 +8937,7 @@
         <v>360</v>
       </c>
       <c r="E273" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="F273" t="s">
         <v>55</v>
@@ -8581,7 +8957,7 @@
         <v>361</v>
       </c>
       <c r="E274" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F274" t="s">
         <v>55</v>
@@ -8601,7 +8977,7 @@
         <v>362</v>
       </c>
       <c r="E275" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F275" t="s">
         <v>55</v>
@@ -8621,7 +8997,7 @@
         <v>363</v>
       </c>
       <c r="E276" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F276" t="s">
         <v>302</v>
@@ -8664,7 +9040,7 @@
         <v>66</v>
       </c>
       <c r="F278" t="s">
-        <v>749</v>
+        <v>728</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.2">
@@ -8681,7 +9057,7 @@
         <v>366</v>
       </c>
       <c r="E279" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F279" t="s">
         <v>55</v>
@@ -8701,7 +9077,7 @@
         <v>367</v>
       </c>
       <c r="E280" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F280" t="s">
         <v>55</v>
@@ -8721,7 +9097,7 @@
         <v>368</v>
       </c>
       <c r="E281" t="s">
-        <v>818</v>
+        <v>797</v>
       </c>
       <c r="F281" t="s">
         <v>55</v>
@@ -8761,7 +9137,7 @@
         <v>371</v>
       </c>
       <c r="E283" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="F283" t="s">
         <v>55</v>
@@ -8781,7 +9157,7 @@
         <v>372</v>
       </c>
       <c r="E284" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F284" t="s">
         <v>55</v>
@@ -8801,7 +9177,7 @@
         <v>373</v>
       </c>
       <c r="E285" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F285" t="s">
         <v>55</v>
@@ -8821,7 +9197,7 @@
         <v>374</v>
       </c>
       <c r="E286" t="s">
-        <v>819</v>
+        <v>798</v>
       </c>
       <c r="F286" t="s">
         <v>55</v>
@@ -8841,7 +9217,7 @@
         <v>375</v>
       </c>
       <c r="E287" t="s">
-        <v>802</v>
+        <v>781</v>
       </c>
       <c r="F287" t="s">
         <v>55</v>
@@ -8861,13 +9237,13 @@
         <v>376</v>
       </c>
       <c r="E288" t="s">
-        <v>819</v>
+        <v>798</v>
       </c>
       <c r="F288" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>2024</v>
       </c>
@@ -8881,13 +9257,13 @@
         <v>377</v>
       </c>
       <c r="E289" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="F289" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>2024</v>
       </c>
@@ -8901,13 +9277,13 @@
         <v>378</v>
       </c>
       <c r="E290" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="F290" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>2024</v>
       </c>
@@ -8921,13 +9297,13 @@
         <v>379</v>
       </c>
       <c r="E291" t="s">
-        <v>801</v>
+        <v>780</v>
       </c>
       <c r="F291" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>2024</v>
       </c>
@@ -8941,13 +9317,13 @@
         <v>380</v>
       </c>
       <c r="E292" t="s">
-        <v>820</v>
+        <v>799</v>
       </c>
       <c r="F292" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>2024</v>
       </c>
@@ -8961,13 +9337,13 @@
         <v>381</v>
       </c>
       <c r="E293" t="s">
-        <v>821</v>
+        <v>800</v>
       </c>
       <c r="F293" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>2024</v>
       </c>
@@ -8987,7 +9363,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>2024</v>
       </c>
@@ -9001,13 +9377,13 @@
         <v>383</v>
       </c>
       <c r="E295" t="s">
-        <v>770</v>
+        <v>749</v>
       </c>
       <c r="F295" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>2024</v>
       </c>
@@ -9021,13 +9397,13 @@
         <v>384</v>
       </c>
       <c r="E296" t="s">
-        <v>777</v>
+        <v>756</v>
       </c>
       <c r="F296" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>2024</v>
       </c>
@@ -9047,7 +9423,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>2024</v>
       </c>
@@ -9061,13 +9437,13 @@
         <v>386</v>
       </c>
       <c r="E298" t="s">
-        <v>787</v>
+        <v>766</v>
       </c>
       <c r="F298" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>2025</v>
       </c>
@@ -9081,13 +9457,16 @@
         <v>388</v>
       </c>
       <c r="E299" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F299" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G299" s="3" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>2025</v>
       </c>
@@ -9101,13 +9480,13 @@
         <v>389</v>
       </c>
       <c r="E300" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F300" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>2025</v>
       </c>
@@ -9121,13 +9500,13 @@
         <v>390</v>
       </c>
       <c r="E301" t="s">
-        <v>822</v>
+        <v>801</v>
       </c>
       <c r="F301" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>2025</v>
       </c>
@@ -9141,13 +9520,13 @@
         <v>391</v>
       </c>
       <c r="E302" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F302" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>2025</v>
       </c>
@@ -9161,13 +9540,13 @@
         <v>392</v>
       </c>
       <c r="E303" t="s">
-        <v>823</v>
+        <v>802</v>
       </c>
       <c r="F303" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>2025</v>
       </c>
@@ -9181,7 +9560,7 @@
         <v>393</v>
       </c>
       <c r="E304" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F304" t="s">
         <v>55</v>
@@ -9201,10 +9580,10 @@
         <v>394</v>
       </c>
       <c r="E305" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F305" t="s">
-        <v>731</v>
+        <v>712</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.2">
@@ -9221,7 +9600,7 @@
         <v>395</v>
       </c>
       <c r="E306" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="F306" t="s">
         <v>300</v>
@@ -9241,7 +9620,7 @@
         <v>396</v>
       </c>
       <c r="E307" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F307" t="s">
         <v>55</v>
@@ -9261,7 +9640,7 @@
         <v>397</v>
       </c>
       <c r="E308" t="s">
-        <v>824</v>
+        <v>803</v>
       </c>
       <c r="F308" t="s">
         <v>55</v>
@@ -9281,7 +9660,7 @@
         <v>398</v>
       </c>
       <c r="E309" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="F309" t="s">
         <v>55</v>
@@ -9301,7 +9680,7 @@
         <v>399</v>
       </c>
       <c r="E310" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="F310" t="s">
         <v>55</v>
@@ -9321,7 +9700,7 @@
         <v>400</v>
       </c>
       <c r="E311" t="s">
-        <v>825</v>
+        <v>804</v>
       </c>
       <c r="F311" t="s">
         <v>55</v>
@@ -9341,7 +9720,7 @@
         <v>401</v>
       </c>
       <c r="E312" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F312" t="s">
         <v>55</v>
@@ -9361,7 +9740,7 @@
         <v>402</v>
       </c>
       <c r="E313" t="s">
-        <v>800</v>
+        <v>779</v>
       </c>
       <c r="F313" t="s">
         <v>55</v>
@@ -9381,7 +9760,7 @@
         <v>403</v>
       </c>
       <c r="E314" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F314" t="s">
         <v>55</v>
@@ -9401,7 +9780,7 @@
         <v>404</v>
       </c>
       <c r="E315" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F315" t="s">
         <v>55</v>
@@ -9421,7 +9800,7 @@
         <v>405</v>
       </c>
       <c r="E316" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F316" t="s">
         <v>55</v>
@@ -9441,7 +9820,7 @@
         <v>540</v>
       </c>
       <c r="E317" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F317" t="s">
         <v>541</v>
@@ -9461,7 +9840,7 @@
         <v>406</v>
       </c>
       <c r="E318" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F318" t="s">
         <v>55</v>
@@ -9481,10 +9860,10 @@
         <v>407</v>
       </c>
       <c r="E319" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F319" t="s">
-        <v>732</v>
+        <v>713</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.2">
@@ -9501,10 +9880,10 @@
         <v>408</v>
       </c>
       <c r="E320" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="F320" t="s">
-        <v>731</v>
+        <v>712</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.2">
@@ -9521,7 +9900,7 @@
         <v>409</v>
       </c>
       <c r="E321" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="F321" t="s">
         <v>55</v>
@@ -9541,7 +9920,7 @@
         <v>410</v>
       </c>
       <c r="E322" t="s">
-        <v>826</v>
+        <v>805</v>
       </c>
       <c r="F322" t="s">
         <v>55</v>
@@ -9561,7 +9940,7 @@
         <v>411</v>
       </c>
       <c r="E323" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="F323" t="s">
         <v>412</v>
@@ -9581,7 +9960,7 @@
         <v>413</v>
       </c>
       <c r="E324" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="F324" t="s">
         <v>55</v>
@@ -9601,10 +9980,10 @@
         <v>414</v>
       </c>
       <c r="E325" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="F325" t="s">
-        <v>738</v>
+        <v>717</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.2">
@@ -9621,7 +10000,7 @@
         <v>415</v>
       </c>
       <c r="E326" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F326" t="s">
         <v>416</v>
@@ -9641,7 +10020,7 @@
         <v>417</v>
       </c>
       <c r="E327" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F327" t="s">
         <v>418</v>
@@ -9661,7 +10040,7 @@
         <v>419</v>
       </c>
       <c r="E328" t="s">
-        <v>811</v>
+        <v>790</v>
       </c>
       <c r="F328" t="s">
         <v>420</v>
@@ -9681,7 +10060,7 @@
         <v>421</v>
       </c>
       <c r="E329" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="F329" t="s">
         <v>422</v>
@@ -9701,7 +10080,7 @@
         <v>423</v>
       </c>
       <c r="E330" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F330" t="s">
         <v>57</v>
@@ -9721,7 +10100,7 @@
         <v>424</v>
       </c>
       <c r="E331" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="F331" t="s">
         <v>425</v>
@@ -9741,7 +10120,7 @@
         <v>426</v>
       </c>
       <c r="E332" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F332" t="s">
         <v>57</v>
@@ -9761,7 +10140,7 @@
         <v>427</v>
       </c>
       <c r="E333" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="F333" t="s">
         <v>57</v>
@@ -9781,7 +10160,7 @@
         <v>428</v>
       </c>
       <c r="E334" t="s">
-        <v>827</v>
+        <v>806</v>
       </c>
       <c r="F334" t="s">
         <v>57</v>
@@ -9801,7 +10180,7 @@
         <v>429</v>
       </c>
       <c r="E335" t="s">
-        <v>809</v>
+        <v>788</v>
       </c>
       <c r="F335" t="s">
         <v>57</v>
@@ -9821,7 +10200,7 @@
         <v>430</v>
       </c>
       <c r="E336" t="s">
-        <v>828</v>
+        <v>807</v>
       </c>
       <c r="F336" t="s">
         <v>503</v>
@@ -9841,7 +10220,7 @@
         <v>431</v>
       </c>
       <c r="E337" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F337" t="s">
         <v>55</v>
@@ -9861,7 +10240,7 @@
         <v>432</v>
       </c>
       <c r="E338" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F338" t="s">
         <v>55</v>
@@ -9881,7 +10260,7 @@
         <v>433</v>
       </c>
       <c r="E339" t="s">
-        <v>829</v>
+        <v>808</v>
       </c>
       <c r="F339" t="s">
         <v>55</v>
@@ -9901,7 +10280,7 @@
         <v>434</v>
       </c>
       <c r="E340" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F340" t="s">
         <v>57</v>
@@ -9921,7 +10300,7 @@
         <v>435</v>
       </c>
       <c r="E341" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F341" t="s">
         <v>55</v>
@@ -9941,7 +10320,7 @@
         <v>436</v>
       </c>
       <c r="E342" t="s">
-        <v>790</v>
+        <v>769</v>
       </c>
       <c r="F342" t="s">
         <v>55</v>
@@ -9961,7 +10340,7 @@
         <v>437</v>
       </c>
       <c r="E343" t="s">
-        <v>811</v>
+        <v>790</v>
       </c>
       <c r="F343" t="s">
         <v>57</v>
@@ -9981,7 +10360,7 @@
         <v>438</v>
       </c>
       <c r="E344" t="s">
-        <v>830</v>
+        <v>809</v>
       </c>
       <c r="F344" t="s">
         <v>55</v>
@@ -10001,7 +10380,7 @@
         <v>439</v>
       </c>
       <c r="E345" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F345" t="s">
         <v>416</v>
@@ -10021,7 +10400,7 @@
         <v>440</v>
       </c>
       <c r="E346" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F346" t="s">
         <v>195</v>
@@ -10041,7 +10420,7 @@
         <v>441</v>
       </c>
       <c r="E347" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F347" t="s">
         <v>442</v>
@@ -10061,7 +10440,7 @@
         <v>443</v>
       </c>
       <c r="E348" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F348" t="s">
         <v>55</v>
@@ -10081,7 +10460,7 @@
         <v>444</v>
       </c>
       <c r="E349" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F349" t="s">
         <v>57</v>
@@ -10101,7 +10480,7 @@
         <v>445</v>
       </c>
       <c r="E350" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F350" t="s">
         <v>55</v>
@@ -10121,7 +10500,7 @@
         <v>446</v>
       </c>
       <c r="E351" t="s">
-        <v>804</v>
+        <v>783</v>
       </c>
       <c r="F351" t="s">
         <v>55</v>
@@ -10141,7 +10520,7 @@
         <v>447</v>
       </c>
       <c r="E352" t="s">
-        <v>831</v>
+        <v>810</v>
       </c>
       <c r="F352" t="s">
         <v>55</v>
@@ -10161,7 +10540,7 @@
         <v>448</v>
       </c>
       <c r="E353" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F353" t="s">
         <v>55</v>
@@ -10181,7 +10560,7 @@
         <v>449</v>
       </c>
       <c r="E354" t="s">
-        <v>810</v>
+        <v>789</v>
       </c>
       <c r="F354" t="s">
         <v>55</v>
@@ -10201,7 +10580,7 @@
         <v>450</v>
       </c>
       <c r="E355" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F355" t="s">
         <v>442</v>
@@ -10221,7 +10600,7 @@
         <v>451</v>
       </c>
       <c r="E356" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="F356" t="s">
         <v>195</v>
@@ -10241,7 +10620,7 @@
         <v>452</v>
       </c>
       <c r="E357" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="F357" t="s">
         <v>55</v>
@@ -10261,7 +10640,7 @@
         <v>453</v>
       </c>
       <c r="E358" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="F358" t="s">
         <v>300</v>
@@ -10281,7 +10660,7 @@
         <v>454</v>
       </c>
       <c r="E359" t="s">
-        <v>832</v>
+        <v>811</v>
       </c>
       <c r="F359" t="s">
         <v>55</v>
@@ -10321,7 +10700,7 @@
         <v>456</v>
       </c>
       <c r="E361" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F361" t="s">
         <v>55</v>
@@ -10341,7 +10720,7 @@
         <v>457</v>
       </c>
       <c r="E362" t="s">
-        <v>833</v>
+        <v>812</v>
       </c>
       <c r="F362" t="s">
         <v>442</v>
@@ -10361,7 +10740,7 @@
         <v>458</v>
       </c>
       <c r="E363" t="s">
-        <v>810</v>
+        <v>789</v>
       </c>
       <c r="F363" t="s">
         <v>55</v>
@@ -10381,7 +10760,7 @@
         <v>459</v>
       </c>
       <c r="E364" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="F364" t="s">
         <v>279</v>
@@ -10401,7 +10780,7 @@
         <v>460</v>
       </c>
       <c r="E365" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F365" t="s">
         <v>55</v>
@@ -10421,7 +10800,7 @@
         <v>461</v>
       </c>
       <c r="E366" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F366" t="s">
         <v>55</v>
@@ -10461,7 +10840,7 @@
         <v>6</v>
       </c>
       <c r="E368" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F368" t="s">
         <v>55</v>
@@ -10481,7 +10860,7 @@
         <v>463</v>
       </c>
       <c r="E369" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F369" t="s">
         <v>55</v>
@@ -10501,7 +10880,7 @@
         <v>464</v>
       </c>
       <c r="E370" t="s">
-        <v>834</v>
+        <v>813</v>
       </c>
       <c r="F370" t="s">
         <v>55</v>
@@ -10521,7 +10900,7 @@
         <v>465</v>
       </c>
       <c r="E371" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F371" t="s">
         <v>55</v>
@@ -10541,7 +10920,7 @@
         <v>466</v>
       </c>
       <c r="E372" t="s">
-        <v>784</v>
+        <v>763</v>
       </c>
       <c r="F372" t="s">
         <v>55</v>
@@ -10561,7 +10940,7 @@
         <v>467</v>
       </c>
       <c r="E373" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F373" t="s">
         <v>55</v>
@@ -10581,7 +10960,7 @@
         <v>468</v>
       </c>
       <c r="E374" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="F374" t="s">
         <v>55</v>
@@ -10601,7 +10980,7 @@
         <v>469</v>
       </c>
       <c r="E375" t="s">
-        <v>835</v>
+        <v>814</v>
       </c>
       <c r="F375" t="s">
         <v>470</v>
@@ -10621,7 +11000,7 @@
         <v>471</v>
       </c>
       <c r="E376" t="s">
-        <v>784</v>
+        <v>763</v>
       </c>
       <c r="F376" t="s">
         <v>55</v>
@@ -10641,7 +11020,7 @@
         <v>472</v>
       </c>
       <c r="E377" t="s">
-        <v>814</v>
+        <v>793</v>
       </c>
       <c r="F377" t="s">
         <v>55</v>
@@ -10664,7 +11043,7 @@
         <v>131</v>
       </c>
       <c r="F378" t="s">
-        <v>738</v>
+        <v>717</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.2">
@@ -10681,7 +11060,7 @@
         <v>474</v>
       </c>
       <c r="E379" t="s">
-        <v>836</v>
+        <v>815</v>
       </c>
       <c r="F379" t="s">
         <v>55</v>
@@ -10701,7 +11080,7 @@
         <v>475</v>
       </c>
       <c r="E380" t="s">
-        <v>819</v>
+        <v>798</v>
       </c>
       <c r="F380" t="s">
         <v>55</v>
@@ -10721,7 +11100,7 @@
         <v>476</v>
       </c>
       <c r="E381" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="F381" t="s">
         <v>55</v>
@@ -10741,7 +11120,7 @@
         <v>477</v>
       </c>
       <c r="E382" t="s">
-        <v>837</v>
+        <v>816</v>
       </c>
       <c r="F382" t="s">
         <v>55</v>
@@ -10761,7 +11140,7 @@
         <v>478</v>
       </c>
       <c r="E383" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="F383" t="s">
         <v>55</v>
@@ -10781,7 +11160,7 @@
         <v>479</v>
       </c>
       <c r="E384" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="F384" t="s">
         <v>55</v>
@@ -10801,7 +11180,7 @@
         <v>480</v>
       </c>
       <c r="E385" t="s">
-        <v>838</v>
+        <v>817</v>
       </c>
       <c r="F385" t="s">
         <v>55</v>
@@ -10841,7 +11220,7 @@
         <v>482</v>
       </c>
       <c r="E387" t="s">
-        <v>836</v>
+        <v>815</v>
       </c>
       <c r="F387" t="s">
         <v>55</v>
@@ -10861,7 +11240,7 @@
         <v>483</v>
       </c>
       <c r="E388" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F388" t="s">
         <v>55</v>
@@ -10881,7 +11260,7 @@
         <v>484</v>
       </c>
       <c r="E389" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="F389" t="s">
         <v>55</v>
@@ -10901,7 +11280,7 @@
         <v>485</v>
       </c>
       <c r="E390" t="s">
-        <v>839</v>
+        <v>818</v>
       </c>
       <c r="F390" t="s">
         <v>55</v>
@@ -10941,10 +11320,10 @@
         <v>487</v>
       </c>
       <c r="E392" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="F392" t="s">
-        <v>738</v>
+        <v>717</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.2">
@@ -10961,7 +11340,7 @@
         <v>488</v>
       </c>
       <c r="E393" t="s">
-        <v>840</v>
+        <v>819</v>
       </c>
       <c r="F393" t="s">
         <v>470</v>
@@ -10981,7 +11360,7 @@
         <v>489</v>
       </c>
       <c r="E394" t="s">
-        <v>841</v>
+        <v>820</v>
       </c>
       <c r="F394" t="s">
         <v>279</v>
@@ -11001,10 +11380,10 @@
         <v>490</v>
       </c>
       <c r="E395" t="s">
-        <v>842</v>
+        <v>821</v>
       </c>
       <c r="F395" t="s">
-        <v>732</v>
+        <v>713</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.2">
@@ -11021,7 +11400,7 @@
         <v>491</v>
       </c>
       <c r="E396" t="s">
-        <v>843</v>
+        <v>822</v>
       </c>
       <c r="F396" t="s">
         <v>57</v>
@@ -11041,7 +11420,7 @@
         <v>492</v>
       </c>
       <c r="E397" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="F397" t="s">
         <v>195</v>
@@ -11064,7 +11443,7 @@
         <v>131</v>
       </c>
       <c r="F398" t="s">
-        <v>733</v>
+        <v>714</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.2">
@@ -11101,10 +11480,10 @@
         <v>496</v>
       </c>
       <c r="E400" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="F400" t="s">
-        <v>737</v>
+        <v>716</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.2">
@@ -11164,7 +11543,7 @@
         <v>131</v>
       </c>
       <c r="F403" t="s">
-        <v>750</v>
+        <v>729</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.2">
@@ -11184,7 +11563,7 @@
         <v>131</v>
       </c>
       <c r="F404" t="s">
-        <v>733</v>
+        <v>714</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.2">
@@ -11201,7 +11580,7 @@
         <v>502</v>
       </c>
       <c r="E405" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="F405" t="s">
         <v>503</v>
@@ -11221,7 +11600,7 @@
         <v>504</v>
       </c>
       <c r="E406" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="F406" t="s">
         <v>341</v>
@@ -11241,10 +11620,10 @@
         <v>505</v>
       </c>
       <c r="E407" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="F407" t="s">
-        <v>751</v>
+        <v>730</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.2">
@@ -11261,10 +11640,10 @@
         <v>506</v>
       </c>
       <c r="E408" t="s">
-        <v>785</v>
+        <v>764</v>
       </c>
       <c r="F408" t="s">
-        <v>752</v>
+        <v>731</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.2">
@@ -11284,7 +11663,7 @@
         <v>131</v>
       </c>
       <c r="F409" t="s">
-        <v>752</v>
+        <v>731</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.2">
@@ -11301,10 +11680,10 @@
         <v>508</v>
       </c>
       <c r="E410" t="s">
-        <v>792</v>
+        <v>771</v>
       </c>
       <c r="F410" t="s">
-        <v>752</v>
+        <v>731</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.2">
@@ -11344,7 +11723,7 @@
         <v>131</v>
       </c>
       <c r="F412" t="s">
-        <v>752</v>
+        <v>731</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.2">
@@ -11364,7 +11743,7 @@
         <v>131</v>
       </c>
       <c r="F413" t="s">
-        <v>734</v>
+        <v>715</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.2">
@@ -11401,7 +11780,7 @@
         <v>513</v>
       </c>
       <c r="E415" t="s">
-        <v>777</v>
+        <v>756</v>
       </c>
       <c r="F415" t="s">
         <v>55</v>
@@ -11421,7 +11800,7 @@
         <v>514</v>
       </c>
       <c r="E416" t="s">
-        <v>811</v>
+        <v>790</v>
       </c>
       <c r="F416" t="s">
         <v>55</v>
@@ -11441,7 +11820,7 @@
         <v>515</v>
       </c>
       <c r="E417" t="s">
-        <v>844</v>
+        <v>823</v>
       </c>
       <c r="F417" t="s">
         <v>55</v>
@@ -11461,7 +11840,7 @@
         <v>516</v>
       </c>
       <c r="E418" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="F418" t="s">
         <v>55</v>
@@ -11481,7 +11860,7 @@
         <v>517</v>
       </c>
       <c r="E419" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F419" t="s">
         <v>55</v>
@@ -11501,7 +11880,7 @@
         <v>518</v>
       </c>
       <c r="E420" t="s">
-        <v>819</v>
+        <v>798</v>
       </c>
       <c r="F420" t="s">
         <v>55</v>
@@ -11521,7 +11900,7 @@
         <v>519</v>
       </c>
       <c r="E421" t="s">
-        <v>845</v>
+        <v>824</v>
       </c>
       <c r="F421" t="s">
         <v>55</v>
@@ -11541,7 +11920,7 @@
         <v>520</v>
       </c>
       <c r="E422" t="s">
-        <v>819</v>
+        <v>798</v>
       </c>
       <c r="F422" t="s">
         <v>55</v>
@@ -11581,7 +11960,7 @@
         <v>522</v>
       </c>
       <c r="E424" t="s">
-        <v>777</v>
+        <v>756</v>
       </c>
       <c r="F424" t="s">
         <v>55</v>
@@ -11621,7 +12000,7 @@
         <v>524</v>
       </c>
       <c r="E426" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="F426" t="s">
         <v>55</v>
@@ -11641,7 +12020,7 @@
         <v>525</v>
       </c>
       <c r="E427" t="s">
-        <v>846</v>
+        <v>825</v>
       </c>
       <c r="F427" t="s">
         <v>55</v>
@@ -11721,7 +12100,7 @@
         <v>529</v>
       </c>
       <c r="E431" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F431" t="s">
         <v>55</v>
@@ -11741,7 +12120,7 @@
         <v>530</v>
       </c>
       <c r="E432" t="s">
-        <v>771</v>
+        <v>750</v>
       </c>
       <c r="F432" t="s">
         <v>55</v>
@@ -11761,7 +12140,7 @@
         <v>531</v>
       </c>
       <c r="E433" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="F433" t="s">
         <v>55</v>
@@ -11781,7 +12160,7 @@
         <v>532</v>
       </c>
       <c r="E434" t="s">
-        <v>837</v>
+        <v>816</v>
       </c>
       <c r="F434" t="s">
         <v>55</v>
@@ -11801,7 +12180,7 @@
         <v>533</v>
       </c>
       <c r="E435" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="F435" t="s">
         <v>55</v>
@@ -11821,10 +12200,10 @@
         <v>534</v>
       </c>
       <c r="E436" t="s">
-        <v>815</v>
+        <v>794</v>
       </c>
       <c r="F436" t="s">
-        <v>731</v>
+        <v>712</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.2">
@@ -11841,10 +12220,10 @@
         <v>535</v>
       </c>
       <c r="E437" t="s">
-        <v>815</v>
+        <v>794</v>
       </c>
       <c r="F437" t="s">
-        <v>732</v>
+        <v>713</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.2">
@@ -11861,7 +12240,7 @@
         <v>536</v>
       </c>
       <c r="E438" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="F438" t="s">
         <v>55</v>
@@ -11881,10 +12260,10 @@
         <v>537</v>
       </c>
       <c r="E439" t="s">
-        <v>834</v>
+        <v>813</v>
       </c>
       <c r="F439" t="s">
-        <v>746</v>
+        <v>725</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.2">
@@ -11941,7 +12320,7 @@
         <v>543</v>
       </c>
       <c r="E442" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="F442" t="s">
         <v>705</v>
@@ -11961,7 +12340,7 @@
         <v>544</v>
       </c>
       <c r="E443" t="s">
-        <v>801</v>
+        <v>780</v>
       </c>
       <c r="F443" t="s">
         <v>706</v>
@@ -11981,7 +12360,7 @@
         <v>545</v>
       </c>
       <c r="E444" t="s">
-        <v>847</v>
+        <v>826</v>
       </c>
       <c r="F444" t="s">
         <v>262</v>
@@ -12021,7 +12400,7 @@
         <v>547</v>
       </c>
       <c r="E446" t="s">
-        <v>792</v>
+        <v>771</v>
       </c>
       <c r="F446" t="s">
         <v>279</v>
@@ -12061,7 +12440,7 @@
         <v>549</v>
       </c>
       <c r="E448" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="F448" t="s">
         <v>55</v>
@@ -12101,7 +12480,7 @@
         <v>551</v>
       </c>
       <c r="E450" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="F450" t="s">
         <v>707</v>
@@ -12121,7 +12500,7 @@
         <v>552</v>
       </c>
       <c r="E451" t="s">
-        <v>837</v>
+        <v>816</v>
       </c>
       <c r="F451" t="s">
         <v>195</v>
@@ -12141,7 +12520,7 @@
         <v>553</v>
       </c>
       <c r="E452" t="s">
-        <v>792</v>
+        <v>771</v>
       </c>
       <c r="F452" t="s">
         <v>55</v>
@@ -12161,7 +12540,7 @@
         <v>554</v>
       </c>
       <c r="E453" t="s">
-        <v>848</v>
+        <v>827</v>
       </c>
       <c r="F453" t="s">
         <v>195</v>
@@ -12184,7 +12563,7 @@
         <v>131</v>
       </c>
       <c r="F454" t="s">
-        <v>753</v>
+        <v>732</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.2">
@@ -12201,7 +12580,7 @@
         <v>556</v>
       </c>
       <c r="E455" t="s">
-        <v>785</v>
+        <v>764</v>
       </c>
       <c r="F455" t="s">
         <v>195</v>
@@ -12261,7 +12640,7 @@
         <v>559</v>
       </c>
       <c r="E458" t="s">
-        <v>849</v>
+        <v>828</v>
       </c>
       <c r="F458" t="s">
         <v>57</v>
@@ -12281,7 +12660,7 @@
         <v>560</v>
       </c>
       <c r="E459" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="F459" t="s">
         <v>57</v>
@@ -12301,7 +12680,7 @@
         <v>561</v>
       </c>
       <c r="E460" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="F460" t="s">
         <v>57</v>
@@ -12341,7 +12720,7 @@
         <v>563</v>
       </c>
       <c r="E462" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="F462" t="s">
         <v>195</v>
@@ -12361,7 +12740,7 @@
         <v>564</v>
       </c>
       <c r="E463" t="s">
-        <v>850</v>
+        <v>829</v>
       </c>
       <c r="F463" t="s">
         <v>55</v>
@@ -12401,7 +12780,7 @@
         <v>566</v>
       </c>
       <c r="E465" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="F465" t="s">
         <v>262</v>
@@ -12441,7 +12820,7 @@
         <v>568</v>
       </c>
       <c r="E467" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="F467" t="s">
         <v>262</v>
@@ -12464,7 +12843,7 @@
         <v>131</v>
       </c>
       <c r="F468" t="s">
-        <v>731</v>
+        <v>712</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.2">
@@ -12481,7 +12860,7 @@
         <v>570</v>
       </c>
       <c r="E469" t="s">
-        <v>828</v>
+        <v>807</v>
       </c>
       <c r="F469" t="s">
         <v>708</v>
@@ -12501,7 +12880,7 @@
         <v>571</v>
       </c>
       <c r="E470" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F470" t="s">
         <v>55</v>
@@ -12521,7 +12900,7 @@
         <v>572</v>
       </c>
       <c r="E471" t="s">
-        <v>851</v>
+        <v>830</v>
       </c>
       <c r="F471" t="s">
         <v>55</v>
@@ -12541,7 +12920,7 @@
         <v>573</v>
       </c>
       <c r="E472" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F472" t="s">
         <v>55</v>
@@ -12561,7 +12940,7 @@
         <v>574</v>
       </c>
       <c r="E473" t="s">
-        <v>801</v>
+        <v>780</v>
       </c>
       <c r="F473" t="s">
         <v>57</v>
@@ -12621,7 +13000,7 @@
         <v>577</v>
       </c>
       <c r="E476" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F476" t="s">
         <v>55</v>
@@ -12641,7 +13020,7 @@
         <v>578</v>
       </c>
       <c r="E477" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="F477" t="s">
         <v>262</v>
@@ -12661,7 +13040,7 @@
         <v>579</v>
       </c>
       <c r="E478" t="s">
-        <v>852</v>
+        <v>831</v>
       </c>
       <c r="F478" t="s">
         <v>55</v>
@@ -12681,7 +13060,7 @@
         <v>580</v>
       </c>
       <c r="E479" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="F479" t="s">
         <v>55</v>
@@ -12701,13 +13080,13 @@
         <v>581</v>
       </c>
       <c r="E480" t="s">
-        <v>810</v>
+        <v>789</v>
       </c>
       <c r="F480" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.2">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="481" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A481">
         <v>2026</v>
       </c>
@@ -12721,13 +13100,13 @@
         <v>582</v>
       </c>
       <c r="E481" t="s">
-        <v>797</v>
+        <v>776</v>
       </c>
       <c r="F481" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.2">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="482" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A482">
         <v>2026</v>
       </c>
@@ -12741,13 +13120,13 @@
         <v>583</v>
       </c>
       <c r="E482" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="F482" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A483">
         <v>2026</v>
       </c>
@@ -12767,7 +13146,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A484">
         <v>2026</v>
       </c>
@@ -12787,7 +13166,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A485">
         <v>2026</v>
       </c>
@@ -12801,13 +13180,13 @@
         <v>586</v>
       </c>
       <c r="E485" t="s">
-        <v>853</v>
+        <v>832</v>
       </c>
       <c r="F485" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.2">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="486" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A486">
         <v>2026</v>
       </c>
@@ -12821,13 +13200,13 @@
         <v>587</v>
       </c>
       <c r="E486" t="s">
-        <v>792</v>
+        <v>771</v>
       </c>
       <c r="F486" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A487">
         <v>2026</v>
       </c>
@@ -12841,13 +13220,13 @@
         <v>588</v>
       </c>
       <c r="E487" t="s">
-        <v>854</v>
+        <v>833</v>
       </c>
       <c r="F487" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A488">
         <v>2026</v>
       </c>
@@ -12861,13 +13240,13 @@
         <v>589</v>
       </c>
       <c r="E488" t="s">
-        <v>131</v>
+        <v>1003</v>
       </c>
       <c r="F488" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A489">
         <v>2026</v>
       </c>
@@ -12881,13 +13260,13 @@
         <v>590</v>
       </c>
       <c r="E489" t="s">
-        <v>855</v>
+        <v>834</v>
       </c>
       <c r="F489" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A490">
         <v>2026</v>
       </c>
@@ -12901,13 +13280,16 @@
         <v>591</v>
       </c>
       <c r="E490" t="s">
-        <v>789</v>
+        <v>768</v>
       </c>
       <c r="F490" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G490" s="3" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="491" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A491">
         <v>2026</v>
       </c>
@@ -12921,13 +13303,16 @@
         <v>592</v>
       </c>
       <c r="E491" t="s">
-        <v>856</v>
+        <v>1002</v>
       </c>
       <c r="F491" s="1" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+      <c r="G491" s="3" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="492" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A492">
         <v>2026</v>
       </c>
@@ -12941,13 +13326,16 @@
         <v>593</v>
       </c>
       <c r="E492" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="F492" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.2">
+        <v>997</v>
+      </c>
+      <c r="G492" s="3" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="493" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A493">
         <v>2026</v>
       </c>
@@ -12961,13 +13349,16 @@
         <v>594</v>
       </c>
       <c r="E493" t="s">
-        <v>850</v>
+        <v>829</v>
       </c>
       <c r="F493" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.2">
+        <v>997</v>
+      </c>
+      <c r="G493" s="3" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="494" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A494">
         <v>2026</v>
       </c>
@@ -12981,13 +13372,16 @@
         <v>595</v>
       </c>
       <c r="E494" t="s">
-        <v>857</v>
+        <v>835</v>
       </c>
       <c r="F494" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G494" s="3" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="495" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A495">
         <v>2026</v>
       </c>
@@ -13001,13 +13395,16 @@
         <v>596</v>
       </c>
       <c r="E495" t="s">
-        <v>785</v>
+        <v>764</v>
       </c>
       <c r="F495" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G495" s="3" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="496" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A496">
         <v>2026</v>
       </c>
@@ -13024,10 +13421,13 @@
         <v>66</v>
       </c>
       <c r="F496" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.2">
+        <v>991</v>
+      </c>
+      <c r="G496" s="3" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="497" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A497">
         <v>2026</v>
       </c>
@@ -13041,13 +13441,16 @@
         <v>598</v>
       </c>
       <c r="E497" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="F497" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.2">
+        <v>732</v>
+      </c>
+      <c r="G497" s="3" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="498" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A498">
         <v>2026</v>
       </c>
@@ -13061,13 +13464,16 @@
         <v>599</v>
       </c>
       <c r="E498" t="s">
-        <v>793</v>
+        <v>772</v>
       </c>
       <c r="F498" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.2">
+        <v>991</v>
+      </c>
+      <c r="G498" s="3" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="499" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A499">
         <v>2026</v>
       </c>
@@ -13081,13 +13487,16 @@
         <v>600</v>
       </c>
       <c r="E499" t="s">
-        <v>834</v>
+        <v>813</v>
       </c>
       <c r="F499" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+      <c r="G499" s="3" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="500" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A500">
         <v>2026</v>
       </c>
@@ -13101,13 +13510,16 @@
         <v>601</v>
       </c>
       <c r="E500" t="s">
-        <v>858</v>
+        <v>836</v>
       </c>
       <c r="F500" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G500" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="501" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A501">
         <v>2026</v>
       </c>
@@ -13121,13 +13533,16 @@
         <v>602</v>
       </c>
       <c r="E501" t="s">
-        <v>859</v>
+        <v>837</v>
       </c>
       <c r="F501" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G501" s="3" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="502" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A502">
         <v>2026</v>
       </c>
@@ -13141,13 +13556,16 @@
         <v>603</v>
       </c>
       <c r="E502" t="s">
-        <v>778</v>
+        <v>747</v>
       </c>
       <c r="F502" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+      <c r="G502" s="3" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="503" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A503">
         <v>2026</v>
       </c>
@@ -13161,13 +13579,16 @@
         <v>604</v>
       </c>
       <c r="E503" t="s">
-        <v>774</v>
+        <v>131</v>
       </c>
       <c r="F503" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.2">
+        <v>985</v>
+      </c>
+      <c r="G503" s="3" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="504" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A504">
         <v>2026</v>
       </c>
@@ -13184,10 +13605,13 @@
         <v>131</v>
       </c>
       <c r="F504" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.2">
+        <v>720</v>
+      </c>
+      <c r="G504" s="3" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="505" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A505">
         <v>2026</v>
       </c>
@@ -13201,13 +13625,16 @@
         <v>606</v>
       </c>
       <c r="E505" t="s">
-        <v>776</v>
+        <v>939</v>
       </c>
       <c r="F505" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.2">
+        <v>981</v>
+      </c>
+      <c r="G505" s="3" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="506" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A506">
         <v>2026</v>
       </c>
@@ -13221,13 +13648,16 @@
         <v>607</v>
       </c>
       <c r="E506" t="s">
-        <v>860</v>
+        <v>838</v>
       </c>
       <c r="F506" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.2">
+        <v>711</v>
+      </c>
+      <c r="G506" s="3" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="507" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A507">
         <v>2026</v>
       </c>
@@ -13241,13 +13671,16 @@
         <v>608</v>
       </c>
       <c r="E507" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F507" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+      <c r="G507" s="3" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="508" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A508">
         <v>2026</v>
       </c>
@@ -13261,13 +13694,16 @@
         <v>609</v>
       </c>
       <c r="E508" t="s">
-        <v>801</v>
+        <v>66</v>
       </c>
       <c r="F508" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G508" s="3" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="509" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A509">
         <v>2026</v>
       </c>
@@ -13281,13 +13717,16 @@
         <v>610</v>
       </c>
       <c r="E509" t="s">
-        <v>803</v>
+        <v>916</v>
       </c>
       <c r="F509" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G509" s="3" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="510" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A510">
         <v>2026</v>
       </c>
@@ -13301,13 +13740,16 @@
         <v>611</v>
       </c>
       <c r="E510" t="s">
-        <v>66</v>
+        <v>776</v>
       </c>
       <c r="F510" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G510" s="3" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="511" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A511">
         <v>2026</v>
       </c>
@@ -13321,13 +13763,16 @@
         <v>612</v>
       </c>
       <c r="E511" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="F511" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G511" s="3" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="512" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A512">
         <v>2026</v>
       </c>
@@ -13341,13 +13786,16 @@
         <v>613</v>
       </c>
       <c r="E512" t="s">
-        <v>830</v>
+        <v>809</v>
       </c>
       <c r="F512" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.2">
+        <v>969</v>
+      </c>
+      <c r="G512" s="3" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="513" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A513">
         <v>2026</v>
       </c>
@@ -13361,13 +13809,16 @@
         <v>614</v>
       </c>
       <c r="E513" t="s">
-        <v>826</v>
+        <v>805</v>
       </c>
       <c r="F513" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G513" s="3" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="514" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A514">
         <v>2026</v>
       </c>
@@ -13381,13 +13832,16 @@
         <v>615</v>
       </c>
       <c r="E514" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F514" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G514" s="3" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="515" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A515">
         <v>2026</v>
       </c>
@@ -13401,13 +13855,16 @@
         <v>616</v>
       </c>
       <c r="E515" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F515" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.2">
+        <v>709</v>
+      </c>
+      <c r="G515" s="3" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="516" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A516">
         <v>2026</v>
       </c>
@@ -13421,13 +13878,16 @@
         <v>617</v>
       </c>
       <c r="E516" t="s">
-        <v>861</v>
+        <v>839</v>
       </c>
       <c r="F516" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+      <c r="G516" s="3" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="517" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A517">
         <v>2026</v>
       </c>
@@ -13441,13 +13901,16 @@
         <v>618</v>
       </c>
       <c r="E517" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F517" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+      <c r="G517" s="3" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="518" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A518">
         <v>2026</v>
       </c>
@@ -13461,13 +13924,16 @@
         <v>619</v>
       </c>
       <c r="E518" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F518" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+      <c r="G518" s="3" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="519" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A519">
         <v>2026</v>
       </c>
@@ -13481,13 +13947,16 @@
         <v>620</v>
       </c>
       <c r="E519" t="s">
-        <v>766</v>
+        <v>746</v>
       </c>
       <c r="F519" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G519" s="3" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="520" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A520">
         <v>2026</v>
       </c>
@@ -13501,13 +13970,16 @@
         <v>621</v>
       </c>
       <c r="E520" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F520" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+      <c r="G520" s="3" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="521" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A521">
         <v>2026</v>
       </c>
@@ -13521,13 +13993,16 @@
         <v>622</v>
       </c>
       <c r="E521" t="s">
-        <v>771</v>
+        <v>750</v>
       </c>
       <c r="F521" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.2">
+        <v>712</v>
+      </c>
+      <c r="G521" s="3" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="522" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A522">
         <v>2026</v>
       </c>
@@ -13541,13 +14016,16 @@
         <v>623</v>
       </c>
       <c r="E522" t="s">
-        <v>766</v>
+        <v>750</v>
       </c>
       <c r="F522" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.2">
+        <v>712</v>
+      </c>
+      <c r="G522" s="3" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="523" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A523">
         <v>2026</v>
       </c>
@@ -13561,13 +14039,16 @@
         <v>624</v>
       </c>
       <c r="E523" t="s">
-        <v>766</v>
+        <v>746</v>
       </c>
       <c r="F523" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G523" s="3" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="524" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A524">
         <v>2026</v>
       </c>
@@ -13581,13 +14062,16 @@
         <v>625</v>
       </c>
       <c r="E524" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="F524" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.2">
+        <v>279</v>
+      </c>
+      <c r="G524" s="3" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="525" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A525">
         <v>2026</v>
       </c>
@@ -13601,13 +14085,16 @@
         <v>626</v>
       </c>
       <c r="E525" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="F525" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.2">
+        <v>958</v>
+      </c>
+      <c r="G525" s="3" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="526" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A526">
         <v>2026</v>
       </c>
@@ -13621,13 +14108,16 @@
         <v>627</v>
       </c>
       <c r="E526" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F526" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G526" s="3" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="527" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A527">
         <v>2026</v>
       </c>
@@ -13641,13 +14131,16 @@
         <v>628</v>
       </c>
       <c r="E527" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F527" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+      <c r="G527" s="3" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="528" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A528">
         <v>2026</v>
       </c>
@@ -13661,13 +14154,16 @@
         <v>629</v>
       </c>
       <c r="E528" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F528" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="529" spans="1:6" x14ac:dyDescent="0.2">
+        <v>970</v>
+      </c>
+      <c r="G528" s="3" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="529" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A529">
         <v>2026</v>
       </c>
@@ -13681,13 +14177,16 @@
         <v>630</v>
       </c>
       <c r="E529" t="s">
-        <v>770</v>
+        <v>954</v>
       </c>
       <c r="F529" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+      <c r="G529" s="3" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="530" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A530">
         <v>2026</v>
       </c>
@@ -13701,13 +14200,16 @@
         <v>631</v>
       </c>
       <c r="E530" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="F530" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.2">
+        <v>952</v>
+      </c>
+      <c r="G530" s="3" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="531" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A531">
         <v>2026</v>
       </c>
@@ -13721,13 +14223,16 @@
         <v>632</v>
       </c>
       <c r="E531" t="s">
-        <v>769</v>
+        <v>949</v>
       </c>
       <c r="F531" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+      <c r="G531" s="3" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="532" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A532">
         <v>2026</v>
       </c>
@@ -13741,13 +14246,16 @@
         <v>633</v>
       </c>
       <c r="E532" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F532" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G532" s="3" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="533" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A533">
         <v>2026</v>
       </c>
@@ -13761,13 +14269,16 @@
         <v>634</v>
       </c>
       <c r="E533" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="F533" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G533" s="3" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="534" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A534">
         <v>2026</v>
       </c>
@@ -13781,13 +14292,16 @@
         <v>635</v>
       </c>
       <c r="E534" t="s">
-        <v>766</v>
+        <v>746</v>
       </c>
       <c r="F534" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G534" s="3" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="535" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A535">
         <v>2026</v>
       </c>
@@ -13801,13 +14315,16 @@
         <v>636</v>
       </c>
       <c r="E535" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="F535" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G535" s="3" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="536" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A536">
         <v>2026</v>
       </c>
@@ -13821,13 +14338,16 @@
         <v>637</v>
       </c>
       <c r="E536" t="s">
-        <v>862</v>
+        <v>840</v>
       </c>
       <c r="F536" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G536" s="3" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="537" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A537">
         <v>2026</v>
       </c>
@@ -13841,13 +14361,16 @@
         <v>638</v>
       </c>
       <c r="E537" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F537" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="538" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G537" s="3" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="538" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A538">
         <v>2026</v>
       </c>
@@ -13861,13 +14384,16 @@
         <v>639</v>
       </c>
       <c r="E538" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F538" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+      <c r="G538" s="3" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="539" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A539">
         <v>2026</v>
       </c>
@@ -13881,13 +14407,16 @@
         <v>640</v>
       </c>
       <c r="E539" t="s">
-        <v>812</v>
+        <v>791</v>
       </c>
       <c r="F539" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G539" s="3" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="540" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A540">
         <v>2026</v>
       </c>
@@ -13901,13 +14430,16 @@
         <v>641</v>
       </c>
       <c r="E540" t="s">
-        <v>776</v>
+        <v>939</v>
       </c>
       <c r="F540" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G540" s="3" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="541" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A541">
         <v>2026</v>
       </c>
@@ -13921,13 +14453,16 @@
         <v>642</v>
       </c>
       <c r="E541" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F541" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G541" s="3" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="542" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A542">
         <v>2026</v>
       </c>
@@ -13941,13 +14476,16 @@
         <v>643</v>
       </c>
       <c r="E542" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F542" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G542" s="3" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="543" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A543">
         <v>2026</v>
       </c>
@@ -13961,13 +14499,16 @@
         <v>644</v>
       </c>
       <c r="E543" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F543" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G543" s="3" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="544" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A544">
         <v>2026</v>
       </c>
@@ -13981,13 +14522,16 @@
         <v>645</v>
       </c>
       <c r="E544" t="s">
-        <v>805</v>
+        <v>784</v>
       </c>
       <c r="F544" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G544" s="3" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="545" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A545">
         <v>2026</v>
       </c>
@@ -14001,13 +14545,16 @@
         <v>646</v>
       </c>
       <c r="E545" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F545" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G545" s="3" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="546" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A546">
         <v>2026</v>
       </c>
@@ -14021,13 +14568,16 @@
         <v>647</v>
       </c>
       <c r="E546" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F546" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="547" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G546" s="3" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="547" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A547">
         <v>2026</v>
       </c>
@@ -14041,13 +14591,16 @@
         <v>648</v>
       </c>
       <c r="E547" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F547" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="548" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G547" s="3" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="548" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A548">
         <v>2026</v>
       </c>
@@ -14061,13 +14614,16 @@
         <v>649</v>
       </c>
       <c r="E548" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F548" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+      <c r="G548" s="3" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="549" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A549">
         <v>2026</v>
       </c>
@@ -14081,13 +14637,16 @@
         <v>650</v>
       </c>
       <c r="E549" t="s">
-        <v>775</v>
+        <v>930</v>
       </c>
       <c r="F549" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G549" s="3" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="550" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A550">
         <v>2026</v>
       </c>
@@ -14106,8 +14665,11 @@
       <c r="F550" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G550" s="3" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="551" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A551">
         <v>2026</v>
       </c>
@@ -14121,13 +14683,16 @@
         <v>652</v>
       </c>
       <c r="E551" t="s">
-        <v>863</v>
+        <v>841</v>
       </c>
       <c r="F551" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G551" s="3" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="552" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A552">
         <v>2026</v>
       </c>
@@ -14146,8 +14711,11 @@
       <c r="F552" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G552" s="3" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="553" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A553">
         <v>2026</v>
       </c>
@@ -14161,13 +14729,16 @@
         <v>654</v>
       </c>
       <c r="E553" t="s">
-        <v>66</v>
+        <v>766</v>
       </c>
       <c r="F553" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G553" s="3" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="554" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A554">
         <v>2026</v>
       </c>
@@ -14181,13 +14752,16 @@
         <v>655</v>
       </c>
       <c r="E554" t="s">
-        <v>864</v>
+        <v>842</v>
       </c>
       <c r="F554" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G554" s="3" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="555" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A555">
         <v>2026</v>
       </c>
@@ -14201,13 +14775,16 @@
         <v>656</v>
       </c>
       <c r="E555" t="s">
-        <v>865</v>
+        <v>922</v>
       </c>
       <c r="F555" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G555" s="3" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="556" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A556">
         <v>2026</v>
       </c>
@@ -14221,13 +14798,16 @@
         <v>657</v>
       </c>
       <c r="E556" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="F556" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+      <c r="G556" s="3" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="557" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A557">
         <v>2026</v>
       </c>
@@ -14241,13 +14821,16 @@
         <v>658</v>
       </c>
       <c r="E557" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F557" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G557" s="3" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="558" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A558">
         <v>2026</v>
       </c>
@@ -14261,13 +14844,16 @@
         <v>659</v>
       </c>
       <c r="E558" t="s">
-        <v>787</v>
+        <v>766</v>
       </c>
       <c r="F558" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G558" s="3" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="559" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A559">
         <v>2026</v>
       </c>
@@ -14281,13 +14867,16 @@
         <v>660</v>
       </c>
       <c r="E559" t="s">
-        <v>66</v>
+        <v>766</v>
       </c>
       <c r="F559" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G559" s="3" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="560" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A560">
         <v>2026</v>
       </c>
@@ -14301,13 +14890,16 @@
         <v>661</v>
       </c>
       <c r="E560" t="s">
-        <v>776</v>
+        <v>916</v>
       </c>
       <c r="F560" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G560" s="3" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="561" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A561">
         <v>2026</v>
       </c>
@@ -14321,13 +14913,16 @@
         <v>662</v>
       </c>
       <c r="E561" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="F561" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G561" s="3" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="562" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A562">
         <v>2026</v>
       </c>
@@ -14341,13 +14936,16 @@
         <v>663</v>
       </c>
       <c r="E562" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F562" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G562" s="3" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="563" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A563">
         <v>2026</v>
       </c>
@@ -14361,13 +14959,16 @@
         <v>664</v>
       </c>
       <c r="E563" t="s">
-        <v>837</v>
+        <v>816</v>
       </c>
       <c r="F563" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.2">
+        <v>971</v>
+      </c>
+      <c r="G563" s="3" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="564" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A564">
         <v>2026</v>
       </c>
@@ -14381,13 +14982,16 @@
         <v>665</v>
       </c>
       <c r="E564" t="s">
-        <v>766</v>
+        <v>911</v>
       </c>
       <c r="F564" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="565" spans="1:6" x14ac:dyDescent="0.2">
+        <v>711</v>
+      </c>
+      <c r="G564" s="3" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="565" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A565">
         <v>2026</v>
       </c>
@@ -14401,13 +15005,16 @@
         <v>666</v>
       </c>
       <c r="E565" t="s">
-        <v>798</v>
+        <v>777</v>
       </c>
       <c r="F565" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G565" s="3" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="566" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A566">
         <v>2026</v>
       </c>
@@ -14421,13 +15028,16 @@
         <v>667</v>
       </c>
       <c r="E566" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F566" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G566" s="3" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="567" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A567">
         <v>2026</v>
       </c>
@@ -14441,13 +15051,16 @@
         <v>668</v>
       </c>
       <c r="E567" t="s">
-        <v>798</v>
+        <v>824</v>
       </c>
       <c r="F567" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G567" s="3" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="568" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A568">
         <v>2026</v>
       </c>
@@ -14461,13 +15074,16 @@
         <v>669</v>
       </c>
       <c r="E568" t="s">
-        <v>866</v>
+        <v>905</v>
       </c>
       <c r="F568" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G568" s="3" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="569" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A569">
         <v>2026</v>
       </c>
@@ -14481,13 +15097,16 @@
         <v>670</v>
       </c>
       <c r="E569" t="s">
-        <v>810</v>
+        <v>789</v>
       </c>
       <c r="F569" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G569" s="3" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="570" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A570">
         <v>2026</v>
       </c>
@@ -14501,13 +15120,16 @@
         <v>671</v>
       </c>
       <c r="E570" t="s">
-        <v>867</v>
+        <v>901</v>
       </c>
       <c r="F570" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+      <c r="G570" s="3" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="571" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A571">
         <v>2026</v>
       </c>
@@ -14521,13 +15143,16 @@
         <v>672</v>
       </c>
       <c r="E571" t="s">
-        <v>66</v>
+        <v>766</v>
       </c>
       <c r="F571" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G571" s="3" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="572" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A572">
         <v>2026</v>
       </c>
@@ -14541,13 +15166,16 @@
         <v>673</v>
       </c>
       <c r="E572" t="s">
-        <v>836</v>
+        <v>815</v>
       </c>
       <c r="F572" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G572" s="3" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="573" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A573">
         <v>2026</v>
       </c>
@@ -14561,13 +15189,16 @@
         <v>674</v>
       </c>
       <c r="E573" t="s">
-        <v>837</v>
+        <v>898</v>
       </c>
       <c r="F573" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G573" s="3" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="574" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A574">
         <v>2026</v>
       </c>
@@ -14581,13 +15212,16 @@
         <v>675</v>
       </c>
       <c r="E574" t="s">
-        <v>868</v>
+        <v>894</v>
       </c>
       <c r="F574" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G574" s="3" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="575" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A575">
         <v>2026</v>
       </c>
@@ -14601,13 +15235,16 @@
         <v>676</v>
       </c>
       <c r="E575" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="F575" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G575" s="3" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="576" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A576">
         <v>2026</v>
       </c>
@@ -14621,13 +15258,16 @@
         <v>677</v>
       </c>
       <c r="E576" t="s">
-        <v>776</v>
+        <v>789</v>
       </c>
       <c r="F576" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G576" s="3" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="577" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A577">
         <v>2026</v>
       </c>
@@ -14641,13 +15281,16 @@
         <v>678</v>
       </c>
       <c r="E577" t="s">
-        <v>798</v>
+        <v>824</v>
       </c>
       <c r="F577" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G577" s="3" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="578" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A578">
         <v>2026</v>
       </c>
@@ -14661,13 +15304,16 @@
         <v>679</v>
       </c>
       <c r="E578" t="s">
-        <v>798</v>
+        <v>824</v>
       </c>
       <c r="F578" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G578" s="3" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="579" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A579">
         <v>2026</v>
       </c>
@@ -14681,13 +15327,16 @@
         <v>680</v>
       </c>
       <c r="E579" t="s">
-        <v>798</v>
+        <v>777</v>
       </c>
       <c r="F579" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G579" s="3" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="580" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A580">
         <v>2026</v>
       </c>
@@ -14701,13 +15350,16 @@
         <v>681</v>
       </c>
       <c r="E580" t="s">
-        <v>66</v>
+        <v>766</v>
       </c>
       <c r="F580" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G580" s="3" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="581" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A581">
         <v>2026</v>
       </c>
@@ -14721,13 +15373,16 @@
         <v>682</v>
       </c>
       <c r="E581" t="s">
-        <v>821</v>
+        <v>800</v>
       </c>
       <c r="F581" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G581" s="3" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="582" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A582">
         <v>2026</v>
       </c>
@@ -14741,13 +15396,16 @@
         <v>683</v>
       </c>
       <c r="E582" t="s">
-        <v>787</v>
+        <v>766</v>
       </c>
       <c r="F582" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G582" s="3" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="583" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A583">
         <v>2026</v>
       </c>
@@ -14761,13 +15419,16 @@
         <v>684</v>
       </c>
       <c r="E583" t="s">
-        <v>787</v>
+        <v>766</v>
       </c>
       <c r="F583" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G583" s="3" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="584" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A584">
         <v>2026</v>
       </c>
@@ -14781,13 +15442,16 @@
         <v>685</v>
       </c>
       <c r="E584" t="s">
-        <v>865</v>
+        <v>789</v>
       </c>
       <c r="F584" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G584" s="3" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="585" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A585">
         <v>2026</v>
       </c>
@@ -14801,13 +15465,16 @@
         <v>686</v>
       </c>
       <c r="E585" t="s">
-        <v>787</v>
+        <v>766</v>
       </c>
       <c r="F585" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G585" s="3" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="586" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A586">
         <v>2026</v>
       </c>
@@ -14821,13 +15488,16 @@
         <v>687</v>
       </c>
       <c r="E586" t="s">
-        <v>787</v>
+        <v>766</v>
       </c>
       <c r="F586" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G586" s="3" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="587" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A587">
         <v>2026</v>
       </c>
@@ -14841,13 +15511,16 @@
         <v>688</v>
       </c>
       <c r="E587" t="s">
-        <v>818</v>
+        <v>797</v>
       </c>
       <c r="F587" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G587" s="3" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="588" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A588">
         <v>2026</v>
       </c>
@@ -14861,13 +15534,16 @@
         <v>689</v>
       </c>
       <c r="E588" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="F588" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G588" s="3" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="589" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A589">
         <v>2026</v>
       </c>
@@ -14881,13 +15557,16 @@
         <v>690</v>
       </c>
       <c r="E589" t="s">
-        <v>869</v>
+        <v>843</v>
       </c>
       <c r="F589" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G589" s="3" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="590" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A590">
         <v>2026</v>
       </c>
@@ -14901,13 +15580,16 @@
         <v>691</v>
       </c>
       <c r="E590" t="s">
-        <v>870</v>
+        <v>844</v>
       </c>
       <c r="F590" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G590" s="3" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="591" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A591">
         <v>2026</v>
       </c>
@@ -14921,13 +15603,16 @@
         <v>692</v>
       </c>
       <c r="E591" t="s">
-        <v>779</v>
+        <v>758</v>
       </c>
       <c r="F591" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="592" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G591" s="3" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="592" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A592">
         <v>2026</v>
       </c>
@@ -14941,13 +15626,16 @@
         <v>693</v>
       </c>
       <c r="E592" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F592" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G592" s="3" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="593" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A593">
         <v>2026</v>
       </c>
@@ -14961,13 +15649,16 @@
         <v>694</v>
       </c>
       <c r="E593" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F593" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G593" s="3" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="594" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A594">
         <v>2026</v>
       </c>
@@ -14981,13 +15672,16 @@
         <v>695</v>
       </c>
       <c r="E594" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="F594" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="595" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G594" s="3" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="595" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A595">
         <v>2026</v>
       </c>
@@ -15001,13 +15695,16 @@
         <v>696</v>
       </c>
       <c r="E595" t="s">
-        <v>798</v>
+        <v>777</v>
       </c>
       <c r="F595" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G595" s="3" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="596" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A596">
         <v>2026</v>
       </c>
@@ -15021,13 +15718,16 @@
         <v>697</v>
       </c>
       <c r="E596" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F596" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.2">
+        <v>874</v>
+      </c>
+      <c r="G596" s="3" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="597" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A597">
         <v>2026</v>
       </c>
@@ -15041,13 +15741,16 @@
         <v>698</v>
       </c>
       <c r="E597" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="F597" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G597" s="3" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="598" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A598">
         <v>2026</v>
       </c>
@@ -15066,8 +15769,11 @@
       <c r="F598" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G598" s="3" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="599" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A599">
         <v>2026</v>
       </c>
@@ -15084,10 +15790,13 @@
         <v>131</v>
       </c>
       <c r="F599" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.2">
+        <v>870</v>
+      </c>
+      <c r="G599" s="3" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="600" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A600">
         <v>2026</v>
       </c>
@@ -15106,8 +15815,11 @@
       <c r="F600" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G600" s="3" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="601" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A601">
         <v>2026</v>
       </c>
@@ -15121,13 +15833,16 @@
         <v>702</v>
       </c>
       <c r="E601" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="F601" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G601" s="3" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="602" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A602">
         <v>2026</v>
       </c>
@@ -15141,14 +15856,146 @@
         <v>703</v>
       </c>
       <c r="E602" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="F602" t="s">
-        <v>262</v>
-      </c>
+        <v>710</v>
+      </c>
+      <c r="G602" s="3" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="603" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G603" s="3"/>
+    </row>
+    <row r="604" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G604" s="3"/>
+    </row>
+    <row r="605" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G605" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F602" xr:uid="{68ABCD33-977E-804C-B8A3-208F8BF35AB9}"/>
+  <hyperlinks>
+    <hyperlink ref="G600" r:id="rId1" xr:uid="{BB30A071-E304-E04A-8D99-74D3F8678553}"/>
+    <hyperlink ref="G601:G602" r:id="rId2" display="https://www.ohdsi.org/2026showcase-161/" xr:uid="{390049AC-FE4A-944E-80BE-62006F82B9D8}"/>
+    <hyperlink ref="G601" r:id="rId3" xr:uid="{BD18CF83-65CA-3F48-BC71-E10D94764034}"/>
+    <hyperlink ref="G602" r:id="rId4" xr:uid="{E116A264-89C9-394B-91D1-7EEE31630933}"/>
+    <hyperlink ref="G599" r:id="rId5" xr:uid="{E741D73C-75A7-F648-AE43-E3612F56DFB7}"/>
+    <hyperlink ref="G598" r:id="rId6" xr:uid="{265776D4-C081-9545-82B7-7CFE7CA05C46}"/>
+    <hyperlink ref="G597" r:id="rId7" xr:uid="{7CDF66CD-37B5-614E-9F0C-803EA2CFE89E}"/>
+    <hyperlink ref="G596" r:id="rId8" xr:uid="{18BECD36-2F17-FB42-8AB0-F37A0A9ED284}"/>
+    <hyperlink ref="G595" r:id="rId9" xr:uid="{A51FF1A8-B08D-F447-8476-0D077EA9B1A0}"/>
+    <hyperlink ref="G594" r:id="rId10" xr:uid="{3DF69915-AAD0-4341-870D-35532C28FCB4}"/>
+    <hyperlink ref="G593" r:id="rId11" xr:uid="{EEA56F4F-1778-E44E-9C45-59465B06948A}"/>
+    <hyperlink ref="G592" r:id="rId12" xr:uid="{57CF6150-3CE9-0841-9A62-EBFFD7092DBD}"/>
+    <hyperlink ref="G591" r:id="rId13" xr:uid="{F733BC2F-8D44-4F4D-AF50-BFC18A02A38D}"/>
+    <hyperlink ref="G590" r:id="rId14" xr:uid="{C4FB86B1-3B1F-8840-B5B3-DAC4E0B142AC}"/>
+    <hyperlink ref="G589" r:id="rId15" xr:uid="{8A919B57-9EF1-C142-A25B-1209441A4980}"/>
+    <hyperlink ref="G588" r:id="rId16" xr:uid="{D0D51337-EB04-6444-94AF-B3F87BD89D1C}"/>
+    <hyperlink ref="G587" r:id="rId17" xr:uid="{CF5C4FD5-9275-9644-A282-ADCD0EB05EC5}"/>
+    <hyperlink ref="G586" r:id="rId18" xr:uid="{76AB3C30-2313-EC46-91C2-7BE6FB13448D}"/>
+    <hyperlink ref="G585" r:id="rId19" xr:uid="{376605BA-A389-6646-AD34-37DEDFEADE56}"/>
+    <hyperlink ref="G584" r:id="rId20" xr:uid="{741532B7-37E7-3345-9613-CE5A5C309568}"/>
+    <hyperlink ref="G583" r:id="rId21" xr:uid="{658B06E5-069D-A142-AE2C-05C1ECE935B6}"/>
+    <hyperlink ref="G582" r:id="rId22" xr:uid="{C6B0EA58-449C-5246-BAA7-54A347B58D16}"/>
+    <hyperlink ref="G581" r:id="rId23" xr:uid="{797977A1-1814-134C-B90B-9C77F92C03F0}"/>
+    <hyperlink ref="G580" r:id="rId24" xr:uid="{CD18AD7B-5615-AA47-9EC4-0E4B7F1A2766}"/>
+    <hyperlink ref="G579" r:id="rId25" xr:uid="{2C71DCDA-B5BD-1343-A1EA-1C2A42676258}"/>
+    <hyperlink ref="G578" r:id="rId26" xr:uid="{B76FF950-2A97-C04D-92A5-188AC614024B}"/>
+    <hyperlink ref="G577" r:id="rId27" xr:uid="{5279B126-0B47-4D47-9C99-463F1D7CE223}"/>
+    <hyperlink ref="G576" r:id="rId28" xr:uid="{E322B405-446B-DA45-ADA8-2268DE1A64BB}"/>
+    <hyperlink ref="G575" r:id="rId29" xr:uid="{C0775634-1F00-0448-9C81-D505E9DC71C4}"/>
+    <hyperlink ref="G574" r:id="rId30" xr:uid="{6DF03F90-A9FF-8744-AA87-57635610DD59}"/>
+    <hyperlink ref="G573" r:id="rId31" xr:uid="{D5358E10-E032-3D46-9625-1E499D767DB4}"/>
+    <hyperlink ref="G572" r:id="rId32" xr:uid="{D97EDB63-EC90-5A47-B9B2-185F1842C722}"/>
+    <hyperlink ref="G571" r:id="rId33" xr:uid="{6DA73727-AA2E-3A4F-AFA4-C2D510E414E5}"/>
+    <hyperlink ref="G570" r:id="rId34" xr:uid="{069FEEF8-1730-8D40-8AFE-4BF1B0216D3C}"/>
+    <hyperlink ref="G569" r:id="rId35" xr:uid="{B5CFD36F-32BB-C440-9C38-B972EDA54FA3}"/>
+    <hyperlink ref="G568" r:id="rId36" xr:uid="{FD16B092-F2CB-7D4C-9B71-21A7BFC47329}"/>
+    <hyperlink ref="G567" r:id="rId37" xr:uid="{FD314786-9193-6240-BBB9-DA7B5B00F47F}"/>
+    <hyperlink ref="G566" r:id="rId38" xr:uid="{54CE4B1B-7C16-244B-8E47-F5B9DECEF6FB}"/>
+    <hyperlink ref="G565" r:id="rId39" xr:uid="{259A8EF5-B3DF-644A-9D9D-6F91B2FECEF8}"/>
+    <hyperlink ref="G564" r:id="rId40" xr:uid="{67A20F16-896F-F142-99B3-886BCB51C843}"/>
+    <hyperlink ref="G563" r:id="rId41" xr:uid="{F791B0F5-BA45-7046-9AC4-56005324C956}"/>
+    <hyperlink ref="G562" r:id="rId42" xr:uid="{DCD42640-868A-1045-ACAD-6E58B3362005}"/>
+    <hyperlink ref="G561" r:id="rId43" xr:uid="{BD40DC6E-7EFB-BF4C-AC60-25937D006EBE}"/>
+    <hyperlink ref="G560" r:id="rId44" xr:uid="{FC5F2D43-2C8A-3A49-83E8-D77D96BB11A3}"/>
+    <hyperlink ref="G559" r:id="rId45" xr:uid="{BBDB939D-3224-3F4B-9B06-F58269F9AAE4}"/>
+    <hyperlink ref="G558" r:id="rId46" xr:uid="{7267BAE2-BB10-2C41-8F50-154E1E3BC317}"/>
+    <hyperlink ref="G557" r:id="rId47" xr:uid="{47477F6D-C1F8-4E4E-BC8D-B83EB1C812B9}"/>
+    <hyperlink ref="G556" r:id="rId48" xr:uid="{D5E6B3F7-4307-C746-BD04-E488A52398A9}"/>
+    <hyperlink ref="G555" r:id="rId49" xr:uid="{DEE116C7-5173-D04F-AD1A-364B67DFCA97}"/>
+    <hyperlink ref="G554" r:id="rId50" xr:uid="{50689C5B-6913-284F-97F0-BFCB8B6A5D14}"/>
+    <hyperlink ref="G553" r:id="rId51" xr:uid="{A1D7FFE6-5ECC-074F-BC42-A1425FE84B22}"/>
+    <hyperlink ref="G552" r:id="rId52" xr:uid="{7CFD3C0E-790E-D341-8C60-56D3D77155B8}"/>
+    <hyperlink ref="G551" r:id="rId53" xr:uid="{6536CEBC-ECBA-924A-8132-423FEB411303}"/>
+    <hyperlink ref="G550" r:id="rId54" xr:uid="{9BECD9F0-BC4D-9445-BB4B-1DE325172166}"/>
+    <hyperlink ref="G549" r:id="rId55" xr:uid="{C44A5EF0-5DA7-3844-81FE-78E4454D94A6}"/>
+    <hyperlink ref="G548" r:id="rId56" xr:uid="{C992848D-A9F9-3346-98D3-E9ACBC4AFDBC}"/>
+    <hyperlink ref="G547" r:id="rId57" xr:uid="{DB3BBF11-4FCB-1A45-8A0F-8A6AD973A273}"/>
+    <hyperlink ref="G546" r:id="rId58" xr:uid="{34A8523C-A5A8-3544-96CC-6B4BBDED5749}"/>
+    <hyperlink ref="G545" r:id="rId59" xr:uid="{B8541D82-4720-9C45-A445-B5F991286E9C}"/>
+    <hyperlink ref="G544" r:id="rId60" xr:uid="{001ABF33-4240-BC4A-B347-6862909EC108}"/>
+    <hyperlink ref="G543" r:id="rId61" xr:uid="{7F8848D3-6B1D-3648-BBB0-FB48A1239F1B}"/>
+    <hyperlink ref="G542" r:id="rId62" xr:uid="{C8AFC2B5-4E4E-B54C-8F63-35C2761CFA46}"/>
+    <hyperlink ref="G541" r:id="rId63" xr:uid="{FDBAD089-20FB-324D-B26F-42336D1C25D8}"/>
+    <hyperlink ref="G540" r:id="rId64" xr:uid="{8BB10C06-C401-A74C-A603-50D9A20CD6FF}"/>
+    <hyperlink ref="G539" r:id="rId65" xr:uid="{FF3E7C7C-E070-8946-B79F-D7D35E974532}"/>
+    <hyperlink ref="G538" r:id="rId66" xr:uid="{AEFE4E47-D531-8345-8418-4F535F57E1B8}"/>
+    <hyperlink ref="G537" r:id="rId67" xr:uid="{8E4B3329-908E-BB45-854E-BE74F9E25682}"/>
+    <hyperlink ref="G536" r:id="rId68" xr:uid="{459DF599-C2B7-2347-BDE0-4ADCC56EF7FD}"/>
+    <hyperlink ref="G535" r:id="rId69" xr:uid="{EE57CE2E-BA7F-6F41-ADB7-98C873046963}"/>
+    <hyperlink ref="G534" r:id="rId70" xr:uid="{8C0B3CB6-541C-9740-BA38-DC5FE1D95CD3}"/>
+    <hyperlink ref="G533" r:id="rId71" xr:uid="{872B2B11-F048-D941-8B33-7C31F97DCF43}"/>
+    <hyperlink ref="G532" r:id="rId72" xr:uid="{DB4CF42F-F0DB-4842-B707-FFD57D88FF31}"/>
+    <hyperlink ref="G531" r:id="rId73" xr:uid="{4287C580-B47D-B840-AF34-299377A502C7}"/>
+    <hyperlink ref="G530" r:id="rId74" xr:uid="{D761D727-41E7-9244-AA30-1BF3ECC19442}"/>
+    <hyperlink ref="G529" r:id="rId75" xr:uid="{6C22AF52-00E7-B74A-9282-BD15B7C75716}"/>
+    <hyperlink ref="G528" r:id="rId76" xr:uid="{585FF0F4-BC37-914A-B563-D1C9DDDBEE64}"/>
+    <hyperlink ref="G527" r:id="rId77" xr:uid="{FA9A9E29-D9D4-3C40-B6E6-00D6A82AB9F0}"/>
+    <hyperlink ref="G526" r:id="rId78" xr:uid="{7C8BF8E8-D21D-ED4F-95C4-1B26405DA401}"/>
+    <hyperlink ref="G525" r:id="rId79" xr:uid="{3B73A47D-0ABE-8B45-9F5B-D052307D1FED}"/>
+    <hyperlink ref="G524" r:id="rId80" xr:uid="{57E8D25C-E4CA-554B-96AE-5E94E9A57F20}"/>
+    <hyperlink ref="G523" r:id="rId81" xr:uid="{69540ACF-AEEC-4246-ADED-4B64C249FB45}"/>
+    <hyperlink ref="G522" r:id="rId82" xr:uid="{1AA86488-788B-3044-A58A-53CEFC6F0EC3}"/>
+    <hyperlink ref="G521" r:id="rId83" xr:uid="{57B7DBEB-14EA-894C-AE6C-CB984155B049}"/>
+    <hyperlink ref="G520" r:id="rId84" xr:uid="{7DE741D6-6FDF-354D-8D6B-626E3C51D5FD}"/>
+    <hyperlink ref="G519" r:id="rId85" xr:uid="{D2873522-9982-9A41-A36C-C328ABFC7A6E}"/>
+    <hyperlink ref="G518" r:id="rId86" xr:uid="{F76C57A2-7F8D-3D42-97AA-667562DB08CE}"/>
+    <hyperlink ref="G517" r:id="rId87" xr:uid="{EF3D3E30-0E8C-264C-825A-B4ABA671A733}"/>
+    <hyperlink ref="G516" r:id="rId88" xr:uid="{C43D5655-D546-6242-8A16-5B1B62896E34}"/>
+    <hyperlink ref="G515" r:id="rId89" xr:uid="{9902E556-FFCE-A540-97D8-09831825DCBF}"/>
+    <hyperlink ref="G514" r:id="rId90" xr:uid="{DA17FC24-4BC6-F849-B3BC-8D5EC8ABE439}"/>
+    <hyperlink ref="G513" r:id="rId91" xr:uid="{2E5169C1-EC27-E747-A7CE-4C346CA8A7FD}"/>
+    <hyperlink ref="G512" r:id="rId92" xr:uid="{7D5368DD-8019-414F-8C7A-E560647C8F3E}"/>
+    <hyperlink ref="G511" r:id="rId93" xr:uid="{41ADBD31-4994-C548-AB8A-D4FFD42BBBAB}"/>
+    <hyperlink ref="G510" r:id="rId94" xr:uid="{4348011D-95A3-D64B-93E2-E50E32CA6EE7}"/>
+    <hyperlink ref="G509" r:id="rId95" xr:uid="{B6A22076-641B-414D-8C95-C14B62799865}"/>
+    <hyperlink ref="G508" r:id="rId96" xr:uid="{F39D3A47-E152-2D42-906F-ECFD77887E23}"/>
+    <hyperlink ref="G507" r:id="rId97" xr:uid="{9162CD0B-E9C6-D24D-BB06-3E984D617F49}"/>
+    <hyperlink ref="G506" r:id="rId98" xr:uid="{D966E434-C49F-4E4F-BAC7-72BDDA5FEA40}"/>
+    <hyperlink ref="G505" r:id="rId99" xr:uid="{44511F25-44F5-2E4B-8BE5-054BADF73961}"/>
+    <hyperlink ref="G504" r:id="rId100" xr:uid="{80D15C89-4EFD-1E44-AF32-C49B1C749194}"/>
+    <hyperlink ref="G503" r:id="rId101" xr:uid="{4964458D-0CE3-1448-AD8B-DA80110311BF}"/>
+    <hyperlink ref="G502" r:id="rId102" xr:uid="{816AD8D8-AA2A-0D41-B145-6DCB5766EDB5}"/>
+    <hyperlink ref="G501" r:id="rId103" xr:uid="{3291505F-71ED-EB48-9D94-C2F5DE46AC06}"/>
+    <hyperlink ref="G500" r:id="rId104" xr:uid="{86F62509-2AAA-7F47-82EE-CFD38720DF70}"/>
+    <hyperlink ref="G499" r:id="rId105" xr:uid="{4401A5F9-7BD7-334D-882B-93D9D8877B5A}"/>
+    <hyperlink ref="G498" r:id="rId106" xr:uid="{9D1517F4-7988-6C47-9F98-C54DD41875E8}"/>
+    <hyperlink ref="G497" r:id="rId107" xr:uid="{59A655C9-EF85-EF4F-9BDB-A1CB1214ED6A}"/>
+    <hyperlink ref="G496" r:id="rId108" xr:uid="{62CFCE30-79EE-4C47-AF0D-635C71EA60E8}"/>
+    <hyperlink ref="G495" r:id="rId109" xr:uid="{9E0D7EA1-2818-014B-A8B0-BF5F0AF2E49D}"/>
+    <hyperlink ref="G494" r:id="rId110" xr:uid="{F513682B-6920-C147-B8C0-D92DD34ADDD4}"/>
+    <hyperlink ref="G493" r:id="rId111" xr:uid="{2DB8B60E-2519-DC48-84DB-2502676C113F}"/>
+    <hyperlink ref="G492" r:id="rId112" xr:uid="{0CB9D54B-E0E1-504C-9313-77935A1960AF}"/>
+    <hyperlink ref="G491" r:id="rId113" xr:uid="{30352F82-573F-D944-91B5-6CE824424194}"/>
+    <hyperlink ref="G490" r:id="rId114" xr:uid="{7729F34C-AC4D-034B-BB36-AB8356EF9487}"/>
+    <hyperlink ref="G2" r:id="rId115" xr:uid="{BA527E30-20D0-C341-BAEA-0CD50C3464EC}"/>
+    <hyperlink ref="G3" r:id="rId116" xr:uid="{7CDCF806-E70B-2842-89A4-0E5D831C737D}"/>
+    <hyperlink ref="G163" r:id="rId117" xr:uid="{680DDF0E-EE5B-9C4F-9AF8-D6F96ECF827D}"/>
+    <hyperlink ref="G299" r:id="rId118" xr:uid="{C755FB30-62CF-2246-A4D4-003FE80CC415}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -15158,21 +16005,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28F9C84F-A2BB-3F44-8D15-45F0F0240D45}">
   <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="37.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>871</v>
+        <v>845</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="B2" t="s">
-        <v>872</v>
+        <v>846</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -15180,31 +16030,31 @@
         <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>873</v>
+        <v>847</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>874</v>
+        <v>848</v>
       </c>
       <c r="B4" t="s">
-        <v>875</v>
+        <v>849</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="B5" t="s">
-        <v>876</v>
+        <v>850</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="B6" t="s">
-        <v>877</v>
+        <v>851</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -15212,31 +16062,31 @@
         <v>66</v>
       </c>
       <c r="B7" t="s">
-        <v>878</v>
+        <v>852</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="B8" t="s">
-        <v>879</v>
+        <v>853</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>880</v>
+        <v>854</v>
       </c>
       <c r="B9" t="s">
-        <v>881</v>
+        <v>855</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="B10" t="s">
-        <v>882</v>
+        <v>856</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -15244,39 +16094,39 @@
         <v>111</v>
       </c>
       <c r="B11" t="s">
-        <v>883</v>
+        <v>857</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="B12" t="s">
-        <v>884</v>
+        <v>858</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>885</v>
+        <v>859</v>
       </c>
       <c r="B13" t="s">
-        <v>886</v>
+        <v>860</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>887</v>
+        <v>861</v>
       </c>
       <c r="B14" t="s">
-        <v>888</v>
+        <v>862</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>790</v>
+        <v>769</v>
       </c>
       <c r="B15" t="s">
-        <v>889</v>
+        <v>863</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -15284,7 +16134,7 @@
         <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>890</v>
+        <v>864</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -15292,7 +16142,7 @@
         <v>131</v>
       </c>
       <c r="B17" t="s">
-        <v>891</v>
+        <v>865</v>
       </c>
     </row>
   </sheetData>
